--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK121"/>
+  <dimension ref="A1:AK122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45926.45833333334</v>
+        <v>45926.47916666666</v>
       </c>
     </row>
     <row r="25">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45926.60416666666</v>
+        <v>45926.58333333334</v>
       </c>
     </row>
     <row r="61">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9486,10 +9486,10 @@
         <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45926.625</v>
+        <v>45926.60416666666</v>
       </c>
     </row>
     <row r="71">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10389,10 +10389,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>45926.63541666666</v>
+        <v>45926.625</v>
       </c>
     </row>
     <row r="90">
@@ -11980,12 +11980,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12100,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>45926.64583333334</v>
+        <v>45926.63541666666</v>
       </c>
     </row>
     <row r="91">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12625,27 +12625,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45926.65625</v>
+        <v>45926.64583333334</v>
       </c>
     </row>
     <row r="96">
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,16 +14124,16 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,16 +14382,16 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -14431,27 +14431,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="AK109" s="3" t="n">
-        <v>45926.66666666666</v>
+        <v>45926.65625</v>
       </c>
     </row>
     <row r="110">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45926.67708333334</v>
+        <v>45926.66666666666</v>
       </c>
     </row>
     <row r="113">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45926.6875</v>
+        <v>45926.67708333334</v>
       </c>
     </row>
     <row r="114">
@@ -15076,27 +15076,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45926.79166666666</v>
+        <v>45926.6875</v>
       </c>
     </row>
     <row r="115">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45926.83333333334</v>
+        <v>45926.79166666666</v>
       </c>
     </row>
     <row r="116">
@@ -15463,12 +15463,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15583,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="AK117" s="3" t="n">
-        <v>45926.875</v>
+        <v>45926.83333333334</v>
       </c>
     </row>
     <row r="118">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15721,12 +15721,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AK119" s="3" t="n">
-        <v>45926.89583333334</v>
+        <v>45926.875</v>
       </c>
     </row>
     <row r="120">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45926.91666666666</v>
+        <v>45926.89583333334</v>
       </c>
     </row>
     <row r="121">
@@ -15979,126 +15979,255 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK121" s="3" t="n">
+        <v>45926.91666666666</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="E122" t="inlineStr">
         <is>
           <t>San Diego Wave</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>Orlando Pride</t>
         </is>
       </c>
-      <c r="G121" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" t="inlineStr">
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L121" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" t="n">
-        <v>0</v>
-      </c>
-      <c r="N121" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" t="n">
-        <v>0</v>
-      </c>
-      <c r="W121" t="n">
-        <v>0</v>
-      </c>
-      <c r="X121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK121" s="3" t="n">
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK122" s="3" t="n">
         <v>45926.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="M74" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="N74" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10002,10 +10002,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.55</v>
+        <v>1.91</v>
       </c>
       <c r="M77" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="N77" t="n">
-        <v>5.3</v>
+        <v>3.8</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10389,10 +10389,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,16 +14124,16 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,16 +14382,16 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB108" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G109" t="n">

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,49 +7764,49 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.6</v>
+        <v>1.82</v>
       </c>
       <c r="M57" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N57" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
         <v>2.1</v>
       </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0</v>
-      </c>
-      <c r="W57" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Z57" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L61" t="n">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10002,10 +10002,10 @@
         <v>0</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10647,10 +10647,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="M92" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="N92" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,16 +13608,16 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,16 +14124,16 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G112" t="n">

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK122"/>
+  <dimension ref="A1:AK123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="M53" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N53" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45926.60416666666</v>
+        <v>45926.58333333334</v>
       </c>
     </row>
     <row r="62">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L62" t="n">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45926.625</v>
+        <v>45926.60416666666</v>
       </c>
     </row>
     <row r="72">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9873,10 +9873,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10647,10 +10647,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11980,12 +11980,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12100,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>45926.63541666666</v>
+        <v>45926.625</v>
       </c>
     </row>
     <row r="91">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45926.64583333334</v>
+        <v>45926.63541666666</v>
       </c>
     </row>
     <row r="92">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12324,10 +12324,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12453,10 +12453,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12754,27 +12754,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
-        <v>45926.65625</v>
+        <v>45926.64583333334</v>
       </c>
     </row>
     <row r="97">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,16 +13608,16 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14560,12 +14560,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,16 +14640,16 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB110" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -14680,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="AK110" s="3" t="n">
-        <v>45926.66666666666</v>
+        <v>45926.65625</v>
       </c>
     </row>
     <row r="111">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45926.67708333334</v>
+        <v>45926.66666666666</v>
       </c>
     </row>
     <row r="114">
@@ -15076,12 +15076,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45926.6875</v>
+        <v>45926.67708333334</v>
       </c>
     </row>
     <row r="115">
@@ -15205,27 +15205,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45926.79166666666</v>
+        <v>45926.6875</v>
       </c>
     </row>
     <row r="116">
@@ -15334,12 +15334,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AK116" s="3" t="n">
-        <v>45926.83333333334</v>
+        <v>45926.79166666666</v>
       </c>
     </row>
     <row r="117">
@@ -15592,12 +15592,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15712,7 +15712,7 @@
         <v>0</v>
       </c>
       <c r="AK118" s="3" t="n">
-        <v>45926.875</v>
+        <v>45926.83333333334</v>
       </c>
     </row>
     <row r="119">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45926.89583333334</v>
+        <v>45926.875</v>
       </c>
     </row>
     <row r="121">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45926.91666666666</v>
+        <v>45926.89583333334</v>
       </c>
     </row>
     <row r="122">
@@ -16108,126 +16108,255 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK122" s="3" t="n">
+        <v>45926.91666666666</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
+      <c r="E123" t="inlineStr">
         <is>
           <t>San Diego Wave</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>Orlando Pride</t>
         </is>
       </c>
-      <c r="G122" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" t="inlineStr">
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L122" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" t="n">
-        <v>0</v>
-      </c>
-      <c r="N122" t="n">
-        <v>0</v>
-      </c>
-      <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" t="n">
-        <v>0</v>
-      </c>
-      <c r="V122" t="n">
-        <v>0</v>
-      </c>
-      <c r="W122" t="n">
-        <v>0</v>
-      </c>
-      <c r="X122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK122" s="3" t="n">
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK123" s="3" t="n">
         <v>45926.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.15</v>
+        <v>2.01</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,49 +7635,49 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.6</v>
+        <v>1.82</v>
       </c>
       <c r="M56" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N56" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="n">
         <v>2.1</v>
       </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0</v>
-      </c>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Z56" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9873,10 +9873,10 @@
         <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12066,10 +12066,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12453,10 +12453,10 @@
         <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12711,10 +12711,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,16 +12963,16 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,16 +14640,16 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB110" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G120" t="n">

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1617,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2133,10 +2133,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3466,27 +3466,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3586,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>45926.47916666666</v>
+        <v>45926.45833333334</v>
       </c>
     </row>
     <row r="25">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3724,27 +3724,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45926.5</v>
+        <v>45926.47916666666</v>
       </c>
     </row>
     <row r="27">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.01</v>
+        <v>4.15</v>
       </c>
       <c r="M32" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="N32" t="n">
-        <v>3.5</v>
+        <v>1.85</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45926.52083333334</v>
+        <v>45926.5</v>
       </c>
     </row>
     <row r="36">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45926.52430555555</v>
+        <v>45926.52083333334</v>
       </c>
     </row>
     <row r="40">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45926.52777777778</v>
+        <v>45926.52430555555</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45926.54166666666</v>
+        <v>45926.52777777778</v>
       </c>
     </row>
     <row r="42">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45926.55208333334</v>
+        <v>45926.54166666666</v>
       </c>
     </row>
     <row r="52">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45926.5625</v>
+        <v>45926.55208333334</v>
       </c>
     </row>
     <row r="53">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="M53" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N53" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7551,10 +7551,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>45926.58333333334</v>
+        <v>45926.5625</v>
       </c>
     </row>
     <row r="56">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="M63" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N63" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8792,17 +8792,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="M67" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N67" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="M69" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N69" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="M70" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N70" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,49 +9570,49 @@
         </is>
       </c>
       <c r="L71" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M71" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N71" t="n">
+        <v>5</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z71" t="n">
         <v>1.7</v>
-      </c>
-      <c r="M71" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N71" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" t="n">
-        <v>0</v>
-      </c>
-      <c r="U71" t="n">
-        <v>0</v>
-      </c>
-      <c r="V71" t="n">
-        <v>0</v>
-      </c>
-      <c r="W71" t="n">
-        <v>0</v>
-      </c>
-      <c r="X71" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>1.67</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11163,10 +11163,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>3.8</v>
+        <v>1.55</v>
       </c>
       <c r="M87" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="N87" t="n">
-        <v>1.83</v>
+        <v>5.3</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,16 +11673,16 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12066,10 +12066,10 @@
         <v>0</v>
       </c>
       <c r="AA90" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB90" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="n">
         <v>0</v>
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,16 +12963,16 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1875,10 +1875,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2133,10 +2133,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.15</v>
+        <v>1.86</v>
       </c>
       <c r="M32" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N32" t="n">
-        <v>1.85</v>
+        <v>3.45</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.77</v>
+        <v>2.22</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="M45" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.81</v>
+        <v>1.96</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="M48" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="N48" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="M62" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N62" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="M63" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N63" t="n">
-        <v>3.85</v>
+        <v>2.4</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8792,17 +8792,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="M66" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N66" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="M67" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N67" t="n">
-        <v>2.4</v>
+        <v>3.85</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="M69" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N69" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="M70" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N70" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="M71" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N71" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="M82" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="N82" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,16 +11028,16 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11163,10 +11163,10 @@
         <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="M84" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N84" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>3.8</v>
+        <v>1.55</v>
       </c>
       <c r="M85" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="N85" t="n">
-        <v>1.83</v>
+        <v>5.3</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,16 +11415,16 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.55</v>
+        <v>3.8</v>
       </c>
       <c r="M87" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="N87" t="n">
-        <v>5.3</v>
+        <v>1.83</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,16 +11673,16 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="M92" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N92" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.39</v>
+        <v>2.7</v>
       </c>
       <c r="M94" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N94" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.11</v>
+        <v>1.9</v>
       </c>
       <c r="M95" t="n">
-        <v>11.5</v>
+        <v>3.7</v>
       </c>
       <c r="N95" t="n">
-        <v>23</v>
+        <v>3.95</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,16 +12705,16 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="M96" t="n">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="N96" t="n">
-        <v>3.95</v>
+        <v>23</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,16 +12834,16 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,14 +13053,14 @@
         </is>
       </c>
       <c r="L98" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M98" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N98" t="n">
         <v>3.75</v>
       </c>
-      <c r="M98" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N98" t="n">
-        <v>1.92</v>
-      </c>
       <c r="O98" t="n">
         <v>0</v>
       </c>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.56</v>
+        <v>3.3</v>
       </c>
       <c r="M101" t="n">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="N101" t="n">
-        <v>4.9</v>
+        <v>2.08</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,16 +13608,16 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G120" t="n">

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1875,10 +1875,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2133,10 +2133,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.13</v>
+        <v>2.36</v>
       </c>
       <c r="M33" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.94</v>
+        <v>1.58</v>
       </c>
       <c r="M45" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N45" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="M51" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N51" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="M62" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N62" t="n">
-        <v>5.3</v>
+        <v>3.85</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8534,17 +8534,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8663,17 +8663,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="M65" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N65" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="M66" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,10 +9054,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="M67" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N67" t="n">
         <v>3.85</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="M68" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N68" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="M69" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N69" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="M70" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N70" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="M71" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N71" t="n">
-        <v>4.9</v>
+        <v>2.1</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11034,10 +11034,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="M84" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="N84" t="n">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,16 +11286,16 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="M85" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="N85" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,16 +11415,16 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA85" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>3.8</v>
+        <v>1.55</v>
       </c>
       <c r="M87" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="N87" t="n">
-        <v>1.83</v>
+        <v>5.3</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,16 +11673,16 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.7</v>
+        <v>1.11</v>
       </c>
       <c r="M94" t="n">
-        <v>3.1</v>
+        <v>11.5</v>
       </c>
       <c r="N94" t="n">
-        <v>2.55</v>
+        <v>23</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12582,10 +12582,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.11</v>
+        <v>2.7</v>
       </c>
       <c r="M96" t="n">
-        <v>11.5</v>
+        <v>3.1</v>
       </c>
       <c r="N96" t="n">
-        <v>23</v>
+        <v>2.55</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,16 +12834,16 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA96" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.85</v>
+        <v>3.75</v>
       </c>
       <c r="M98" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N98" t="n">
-        <v>3.75</v>
+        <v>1.92</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,16 +13608,16 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="M105" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="N105" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1875,10 +1875,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2133,10 +2133,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.15</v>
+        <v>2.06</v>
       </c>
       <c r="M28" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="N28" t="n">
-        <v>1.85</v>
+        <v>3.26</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.13</v>
+        <v>2.42</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="N35" t="n">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="M42" t="n">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="N42" t="n">
-        <v>2.95</v>
+        <v>3.45</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.58</v>
+        <v>2.43</v>
       </c>
       <c r="M45" t="n">
-        <v>4.2</v>
+        <v>3.81</v>
       </c>
       <c r="N45" t="n">
-        <v>4.8</v>
+        <v>2.24</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="M47" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="N47" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,49 +8280,49 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.6</v>
+        <v>1.82</v>
       </c>
       <c r="M61" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N61" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="n">
         <v>2.1</v>
       </c>
-      <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Z61" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="M62" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N62" t="n">
-        <v>3.85</v>
+        <v>2.4</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8534,17 +8534,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8670,10 +8670,10 @@
         <v>1.68</v>
       </c>
       <c r="M64" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N64" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="M65" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N65" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8921,17 +8921,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,49 +9183,49 @@
         </is>
       </c>
       <c r="L68" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M68" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N68" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z68" t="n">
         <v>1.68</v>
-      </c>
-      <c r="M68" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N68" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" t="n">
-        <v>0</v>
-      </c>
-      <c r="W68" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>1.73</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="M69" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N69" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="M70" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N70" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.3</v>
+        <v>1.65</v>
       </c>
       <c r="M71" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N71" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="M73" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N73" t="n">
-        <v>3.9</v>
+        <v>1.83</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="M76" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="N76" t="n">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,16 +10254,16 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="M77" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="N77" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="M84" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="N84" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,16 +11286,16 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,16 +11544,16 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11679,10 +11679,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12150,10 +12150,10 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="M91" t="n">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="N91" t="n">
         <v>1.75</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.39</v>
+        <v>1.08</v>
       </c>
       <c r="M92" t="n">
-        <v>3.25</v>
+        <v>12</v>
       </c>
       <c r="N92" t="n">
-        <v>2.8</v>
+        <v>19</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12324,10 +12324,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12582,10 +12582,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.9</v>
+        <v>2.39</v>
       </c>
       <c r="M95" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N95" t="n">
-        <v>3.95</v>
+        <v>2.8</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="M96" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="N96" t="n">
-        <v>2.55</v>
+        <v>3.95</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.24</v>
+        <v>1.78</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,16 +12963,16 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="M100" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="N100" t="n">
-        <v>2.25</v>
+        <v>5.6</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,7 +13350,7 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Z100" t="n">
         <v>2.1</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="M104" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="N104" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.4</v>
+        <v>2.19</v>
       </c>
       <c r="M111" t="n">
-        <v>3.45</v>
+        <v>3.29</v>
       </c>
       <c r="N111" t="n">
-        <v>2.85</v>
+        <v>3.23</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G118" t="n">

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.57</v>
+        <v>2.09</v>
       </c>
       <c r="M50" t="n">
-        <v>3.93</v>
+        <v>3.47</v>
       </c>
       <c r="N50" t="n">
-        <v>4.33</v>
+        <v>2.83</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.44</v>
+        <v>1.68</v>
       </c>
       <c r="M62" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N62" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.62</v>
+        <v>2.44</v>
       </c>
       <c r="M63" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="M64" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="N64" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8792,17 +8792,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8921,17 +8921,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="M67" t="n">
         <v>3.65</v>
       </c>
       <c r="N67" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="M69" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N69" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="M70" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N70" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="M71" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N71" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10260,10 +10260,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="M77" t="n">
-        <v>4.1</v>
+        <v>3.13</v>
       </c>
       <c r="N77" t="n">
-        <v>5.6</v>
+        <v>3.53</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,16 +10899,16 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="M82" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N82" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,16 +11544,16 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11937,10 +11937,10 @@
         <v>0</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12324,10 +12324,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="M93" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N93" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.39</v>
+        <v>1.08</v>
       </c>
       <c r="M95" t="n">
-        <v>3.25</v>
+        <v>12</v>
       </c>
       <c r="N95" t="n">
-        <v>2.8</v>
+        <v>19</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12711,10 +12711,10 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,16 +12963,16 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="M99" t="n">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="N99" t="n">
-        <v>5.4</v>
+        <v>2.25</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="Z99" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="M102" t="n">
-        <v>3.65</v>
+        <v>4.15</v>
       </c>
       <c r="N102" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,16 +14124,16 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3.45</v>
+        <v>1.55</v>
       </c>
       <c r="M108" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="N108" t="n">
-        <v>2.15</v>
+        <v>5.6</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G118" t="n">

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK123"/>
+  <dimension ref="A1:AK126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1875,10 +1875,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3595,27 +3595,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45926.47916666666</v>
+        <v>45926.45833333334</v>
       </c>
     </row>
     <row r="26">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45926.47916666666</v>
+        <v>45926.45833333334</v>
       </c>
     </row>
     <row r="27">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45926.5</v>
+        <v>45926.45833333334</v>
       </c>
     </row>
     <row r="28">
@@ -3982,27 +3982,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45926.5</v>
+        <v>45926.47916666666</v>
       </c>
     </row>
     <row r="29">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45926.5</v>
+        <v>45926.47916666666</v>
       </c>
     </row>
     <row r="30">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="N30" t="n">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.66</v>
+        <v>2.35</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.22</v>
+        <v>1.6</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.06</v>
+        <v>3.75</v>
       </c>
       <c r="M32" t="n">
-        <v>3.05</v>
+        <v>3.51</v>
       </c>
       <c r="N32" t="n">
-        <v>3.26</v>
+        <v>1.93</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5014,27 +5014,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45926.52083333334</v>
+        <v>45926.5</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45926.52083333334</v>
+        <v>45926.5</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45926.52083333334</v>
+        <v>45926.5</v>
       </c>
     </row>
     <row r="39">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45926.52430555555</v>
+        <v>45926.52083333334</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45926.52777777778</v>
+        <v>45926.52083333334</v>
       </c>
     </row>
     <row r="42">
@@ -5788,27 +5788,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45926.54166666666</v>
+        <v>45926.52083333334</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45926.54166666666</v>
+        <v>45926.52430555555</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45926.54166666666</v>
+        <v>45926.52777777778</v>
       </c>
     </row>
     <row r="45">
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,49 +6474,49 @@
         </is>
       </c>
       <c r="L47" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z47" t="n">
         <v>1.75</v>
-      </c>
-      <c r="M47" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="N47" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.91</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.57</v>
+        <v>2.09</v>
       </c>
       <c r="M48" t="n">
-        <v>3.93</v>
+        <v>3.47</v>
       </c>
       <c r="N48" t="n">
-        <v>4.33</v>
+        <v>2.83</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.43</v>
+        <v>1.75</v>
       </c>
       <c r="M49" t="n">
-        <v>3.81</v>
+        <v>3.53</v>
       </c>
       <c r="N49" t="n">
-        <v>2.24</v>
+        <v>3.78</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.09</v>
+        <v>1.34</v>
       </c>
       <c r="M50" t="n">
-        <v>3.47</v>
+        <v>5.1</v>
       </c>
       <c r="N50" t="n">
-        <v>2.83</v>
+        <v>5.7</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6906,10 +6906,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45926.55208333334</v>
+        <v>45926.54166666666</v>
       </c>
     </row>
     <row r="53">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45926.5625</v>
+        <v>45926.54166666666</v>
       </c>
     </row>
     <row r="54">
@@ -7336,27 +7336,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45926.5625</v>
+        <v>45926.54166666666</v>
       </c>
     </row>
     <row r="55">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7551,10 +7551,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>45926.5625</v>
+        <v>45926.55208333334</v>
       </c>
     </row>
     <row r="56">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7680,10 +7680,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7714,7 +7714,7 @@
         <v>0</v>
       </c>
       <c r="AK56" s="3" t="n">
-        <v>45926.58333333334</v>
+        <v>45926.5625</v>
       </c>
     </row>
     <row r="57">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45926.58333333334</v>
+        <v>45926.5625</v>
       </c>
     </row>
     <row r="58">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45926.58333333334</v>
+        <v>45926.5625</v>
       </c>
     </row>
     <row r="59">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45926.60416666666</v>
+        <v>45926.58333333334</v>
       </c>
     </row>
     <row r="63">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45926.60416666666</v>
+        <v>45926.58333333334</v>
       </c>
     </row>
     <row r="64">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45926.60416666666</v>
+        <v>45926.58333333334</v>
       </c>
     </row>
     <row r="65">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8792,17 +8792,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="M66" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N66" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="M68" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N68" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9437,17 +9437,17 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.33</v>
+        <v>1.68</v>
       </c>
       <c r="M72" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N72" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.74</v>
+        <v>1.52</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45926.625</v>
+        <v>45926.60416666666</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45926.625</v>
+        <v>45926.60416666666</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45926.625</v>
+        <v>45926.60416666666</v>
       </c>
     </row>
     <row r="75">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="M77" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="N77" t="n">
-        <v>3.53</v>
+        <v>2.9</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="M81" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="N81" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,16 +10899,16 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,16 +11157,16 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M89" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="N89" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,16 +11931,16 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12109,12 +12109,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="M91" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="N91" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45926.63541666666</v>
+        <v>45926.625</v>
       </c>
     </row>
     <row r="92">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45926.64583333334</v>
+        <v>45926.625</v>
       </c>
     </row>
     <row r="93">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45926.64583333334</v>
+        <v>45926.625</v>
       </c>
     </row>
     <row r="94">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.7</v>
+        <v>3.75</v>
       </c>
       <c r="M94" t="n">
-        <v>3.1</v>
+        <v>3.56</v>
       </c>
       <c r="N94" t="n">
-        <v>2.55</v>
+        <v>1.75</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45926.64583333334</v>
+        <v>45926.63541666666</v>
       </c>
     </row>
     <row r="95">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.08</v>
+        <v>1.93</v>
       </c>
       <c r="M95" t="n">
-        <v>12</v>
+        <v>3.41</v>
       </c>
       <c r="N95" t="n">
-        <v>19</v>
+        <v>3.23</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,16 +12705,16 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA95" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="M96" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N96" t="n">
-        <v>3.95</v>
+        <v>2.55</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="Z96" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12883,12 +12883,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45926.65625</v>
+        <v>45926.64583333334</v>
       </c>
     </row>
     <row r="98">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13098,10 +13098,10 @@
         <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45926.65625</v>
+        <v>45926.64583333334</v>
       </c>
     </row>
     <row r="99">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>3</v>
+        <v>2.39</v>
       </c>
       <c r="M99" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N99" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45926.65625</v>
+        <v>45926.64583333334</v>
       </c>
     </row>
     <row r="100">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,16 +13995,16 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,16 +14124,16 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="M108" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="N108" t="n">
-        <v>5.6</v>
+        <v>2.15</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="Z108" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14689,27 +14689,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45926.66666666666</v>
+        <v>45926.65625</v>
       </c>
     </row>
     <row r="112">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.19</v>
+        <v>7.2</v>
       </c>
       <c r="M112" t="n">
-        <v>3.29</v>
+        <v>4.8</v>
       </c>
       <c r="N112" t="n">
-        <v>3.23</v>
+        <v>1.35</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45926.66666666666</v>
+        <v>45926.65625</v>
       </c>
     </row>
     <row r="113">
@@ -14947,27 +14947,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45926.66666666666</v>
+        <v>45926.65625</v>
       </c>
     </row>
     <row r="114">
@@ -15076,12 +15076,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.12</v>
+        <v>2.19</v>
       </c>
       <c r="M114" t="n">
-        <v>7.8</v>
+        <v>3.29</v>
       </c>
       <c r="N114" t="n">
-        <v>21</v>
+        <v>3.23</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45926.67708333334</v>
+        <v>45926.66666666666</v>
       </c>
     </row>
     <row r="115">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45926.6875</v>
+        <v>45926.66666666666</v>
       </c>
     </row>
     <row r="116">
@@ -15334,12 +15334,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AK116" s="3" t="n">
-        <v>45926.79166666666</v>
+        <v>45926.66666666666</v>
       </c>
     </row>
     <row r="117">
@@ -15463,27 +15463,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15583,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="AK117" s="3" t="n">
-        <v>45926.83333333334</v>
+        <v>45926.67708333334</v>
       </c>
     </row>
     <row r="118">
@@ -15592,27 +15592,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15712,7 +15712,7 @@
         <v>0</v>
       </c>
       <c r="AK118" s="3" t="n">
-        <v>45926.83333333334</v>
+        <v>45926.6875</v>
       </c>
     </row>
     <row r="119">
@@ -15721,12 +15721,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AK119" s="3" t="n">
-        <v>45926.875</v>
+        <v>45926.79166666666</v>
       </c>
     </row>
     <row r="120">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45926.875</v>
+        <v>45926.83333333334</v>
       </c>
     </row>
     <row r="121">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45926.89583333334</v>
+        <v>45926.83333333334</v>
       </c>
     </row>
     <row r="122">
@@ -16108,12 +16108,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45926.91666666666</v>
+        <v>45926.875</v>
       </c>
     </row>
     <row r="123">
@@ -16237,126 +16237,513 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Kansas City</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Chicago Red Stars</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK123" s="3" t="n">
+        <v>45926.875</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Austin II</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Portland Timbers II</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK124" s="3" t="n">
+        <v>45926.89583333334</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK125" s="3" t="n">
+        <v>45926.91666666666</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E126" t="inlineStr">
         <is>
           <t>San Diego Wave</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>Orlando Pride</t>
         </is>
       </c>
-      <c r="G123" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="inlineStr">
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L123" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" t="n">
-        <v>0</v>
-      </c>
-      <c r="N123" t="n">
-        <v>0</v>
-      </c>
-      <c r="O123" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" t="n">
-        <v>0</v>
-      </c>
-      <c r="W123" t="n">
-        <v>0</v>
-      </c>
-      <c r="X123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK123" s="3" t="n">
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK126" s="3" t="n">
         <v>45926.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK126"/>
+  <dimension ref="A1:AK125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45926.45833333334</v>
+        <v>45926.47916666666</v>
       </c>
     </row>
     <row r="28">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45926.47916666666</v>
+        <v>45926.5</v>
       </c>
     </row>
     <row r="30">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.42</v>
+        <v>3.75</v>
       </c>
       <c r="M33" t="n">
-        <v>3.29</v>
+        <v>3.51</v>
       </c>
       <c r="N33" t="n">
-        <v>2.84</v>
+        <v>1.93</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="M36" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="N36" t="n">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.66</v>
+        <v>2.35</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.22</v>
+        <v>1.6</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45926.5</v>
+        <v>45926.52083333334</v>
       </c>
     </row>
     <row r="39">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45926.52083333334</v>
+        <v>45926.52430555555</v>
       </c>
     </row>
     <row r="43">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45926.52430555555</v>
+        <v>45926.52777777778</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45926.52777777778</v>
+        <v>45926.54166666666</v>
       </c>
     </row>
     <row r="45">
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.09</v>
+        <v>1.34</v>
       </c>
       <c r="M48" t="n">
-        <v>3.47</v>
+        <v>5.1</v>
       </c>
       <c r="N48" t="n">
-        <v>2.83</v>
+        <v>5.7</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6648,10 +6648,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6906,10 +6906,10 @@
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.43</v>
+        <v>1.57</v>
       </c>
       <c r="M51" t="n">
-        <v>3.81</v>
+        <v>3.93</v>
       </c>
       <c r="N51" t="n">
-        <v>2.24</v>
+        <v>4.33</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.57</v>
+        <v>2.43</v>
       </c>
       <c r="M52" t="n">
-        <v>3.93</v>
+        <v>3.81</v>
       </c>
       <c r="N52" t="n">
-        <v>4.33</v>
+        <v>2.24</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7336,27 +7336,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45926.54166666666</v>
+        <v>45926.55208333334</v>
       </c>
     </row>
     <row r="55">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7551,10 +7551,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>45926.55208333334</v>
+        <v>45926.5625</v>
       </c>
     </row>
     <row r="56">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7680,10 +7680,10 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45926.5625</v>
+        <v>45926.58333333334</v>
       </c>
     </row>
     <row r="59">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45926.58333333334</v>
+        <v>45926.60416666666</v>
       </c>
     </row>
     <row r="65">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="M65" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N65" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.65</v>
+        <v>3.3</v>
       </c>
       <c r="M66" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.62</v>
+        <v>2.44</v>
       </c>
       <c r="M67" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N67" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="M69" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N69" t="n">
         <v>3.85</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9437,17 +9437,17 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="M71" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N71" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9695,17 +9695,17 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.44</v>
+        <v>1.65</v>
       </c>
       <c r="M73" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N73" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45926.60416666666</v>
+        <v>45926.625</v>
       </c>
     </row>
     <row r="75">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.33</v>
+        <v>3.8</v>
       </c>
       <c r="M77" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N77" t="n">
-        <v>2.9</v>
+        <v>1.83</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.09</v>
+        <v>1.67</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.74</v>
+        <v>2.07</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.7</v>
+        <v>1.52</v>
       </c>
       <c r="M80" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="N80" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,16 +10770,16 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10905,10 +10905,10 @@
         <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="M83" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="N83" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,16 +11157,16 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="M89" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="N89" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12367,12 +12367,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45926.625</v>
+        <v>45926.63541666666</v>
       </c>
     </row>
     <row r="94">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.75</v>
+        <v>1.08</v>
       </c>
       <c r="M94" t="n">
-        <v>3.56</v>
+        <v>12</v>
       </c>
       <c r="N94" t="n">
-        <v>1.75</v>
+        <v>19</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12582,10 +12582,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45926.63541666666</v>
+        <v>45926.64583333334</v>
       </c>
     </row>
     <row r="95">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="M95" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="N95" t="n">
-        <v>3.23</v>
+        <v>3.11</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="Z95" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="M96" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N96" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="M97" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="N97" t="n">
-        <v>3.11</v>
+        <v>3.23</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.08</v>
+        <v>2.65</v>
       </c>
       <c r="M98" t="n">
-        <v>12</v>
+        <v>3.17</v>
       </c>
       <c r="N98" t="n">
-        <v>19</v>
+        <v>2.66</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13141,27 +13141,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45926.64583333334</v>
+        <v>45926.65625</v>
       </c>
     </row>
     <row r="100">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,16 +13350,16 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="M103" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N103" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,16 +13995,16 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3.45</v>
+        <v>1.6</v>
       </c>
       <c r="M108" t="n">
-        <v>3.35</v>
+        <v>4.15</v>
       </c>
       <c r="N108" t="n">
-        <v>2.15</v>
+        <v>5.4</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="M111" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N111" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="Z111" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>7.2</v>
+        <v>1.85</v>
       </c>
       <c r="M112" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="N112" t="n">
-        <v>1.35</v>
+        <v>4.2</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="Z112" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45926.65625</v>
+        <v>45926.66666666666</v>
       </c>
     </row>
     <row r="114">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15334,27 +15334,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AK116" s="3" t="n">
-        <v>45926.66666666666</v>
+        <v>45926.67708333334</v>
       </c>
     </row>
     <row r="117">
@@ -15463,12 +15463,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15583,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="AK117" s="3" t="n">
-        <v>45926.67708333334</v>
+        <v>45926.6875</v>
       </c>
     </row>
     <row r="118">
@@ -15592,27 +15592,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15712,7 +15712,7 @@
         <v>0</v>
       </c>
       <c r="AK118" s="3" t="n">
-        <v>45926.6875</v>
+        <v>45926.79166666666</v>
       </c>
     </row>
     <row r="119">
@@ -15721,12 +15721,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AK119" s="3" t="n">
-        <v>45926.79166666666</v>
+        <v>45926.83333333334</v>
       </c>
     </row>
     <row r="120">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45926.83333333334</v>
+        <v>45926.875</v>
       </c>
     </row>
     <row r="122">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16237,12 +16237,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45926.875</v>
+        <v>45926.89583333334</v>
       </c>
     </row>
     <row r="124">
@@ -16366,12 +16366,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="AK124" s="3" t="n">
-        <v>45926.89583333334</v>
+        <v>45926.91666666666</v>
       </c>
     </row>
     <row r="125">
@@ -16495,12 +16495,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16615,135 +16615,6 @@
         <v>0</v>
       </c>
       <c r="AK125" s="3" t="n">
-        <v>45926.91666666666</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
-        <v>45926</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Orlando Pride</t>
-        </is>
-      </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L126" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" t="n">
-        <v>0</v>
-      </c>
-      <c r="N126" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" t="n">
-        <v>0</v>
-      </c>
-      <c r="U126" t="n">
-        <v>0</v>
-      </c>
-      <c r="V126" t="n">
-        <v>0</v>
-      </c>
-      <c r="W126" t="n">
-        <v>0</v>
-      </c>
-      <c r="X126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK126" s="3" t="n">
         <v>45926.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="M13" t="n">
-        <v>3.65</v>
+        <v>7.7</v>
       </c>
       <c r="N13" t="n">
-        <v>4.15</v>
+        <v>16</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.42</v>
+        <v>1.86</v>
       </c>
       <c r="M29" t="n">
-        <v>3.29</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>2.84</v>
+        <v>3.45</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.75</v>
+        <v>2.06</v>
       </c>
       <c r="M33" t="n">
-        <v>3.51</v>
+        <v>3.05</v>
       </c>
       <c r="N33" t="n">
-        <v>1.93</v>
+        <v>3.26</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.86</v>
+        <v>2.42</v>
       </c>
       <c r="M35" t="n">
-        <v>3.65</v>
+        <v>3.29</v>
       </c>
       <c r="N35" t="n">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.09</v>
+        <v>2.43</v>
       </c>
       <c r="M44" t="n">
-        <v>3.47</v>
+        <v>3.81</v>
       </c>
       <c r="N44" t="n">
-        <v>2.83</v>
+        <v>2.24</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6390,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.89</v>
+        <v>2.09</v>
       </c>
       <c r="M47" t="n">
-        <v>3.34</v>
+        <v>3.47</v>
       </c>
       <c r="N47" t="n">
-        <v>3.45</v>
+        <v>2.83</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6648,10 +6648,10 @@
         <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.43</v>
+        <v>1.89</v>
       </c>
       <c r="M52" t="n">
-        <v>3.81</v>
+        <v>3.34</v>
       </c>
       <c r="N52" t="n">
-        <v>2.24</v>
+        <v>3.45</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7551,10 +7551,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.94</v>
+        <v>1.74</v>
       </c>
       <c r="M57" t="n">
-        <v>3.97</v>
+        <v>3.75</v>
       </c>
       <c r="N57" t="n">
-        <v>3.32</v>
+        <v>4.4</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,16 +7803,16 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.68</v>
+        <v>2.44</v>
       </c>
       <c r="M64" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N64" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="M65" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N65" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.3</v>
+        <v>1.65</v>
       </c>
       <c r="M66" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N66" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="M67" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N67" t="n">
-        <v>2.4</v>
+        <v>3.85</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="M68" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N68" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="M69" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N69" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="M70" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N70" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.62</v>
+        <v>3.3</v>
       </c>
       <c r="M71" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N71" t="n">
-        <v>5.3</v>
+        <v>2.1</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="M73" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N73" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="M77" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N77" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,16 +10770,16 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="M83" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="N83" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,16 +11157,16 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.7</v>
+        <v>1.52</v>
       </c>
       <c r="M87" t="n">
-        <v>3.35</v>
+        <v>4.6</v>
       </c>
       <c r="N87" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,16 +11673,16 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,55 +12279,55 @@
         </is>
       </c>
       <c r="L92" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M92" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N92" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="n">
+        <v>0</v>
+      </c>
+      <c r="V92" t="n">
+        <v>0</v>
+      </c>
+      <c r="W92" t="n">
+        <v>0</v>
+      </c>
+      <c r="X92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB92" t="n">
         <v>1.6</v>
-      </c>
-      <c r="M92" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N92" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0</v>
-      </c>
-      <c r="S92" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" t="n">
-        <v>0</v>
-      </c>
-      <c r="U92" t="n">
-        <v>0</v>
-      </c>
-      <c r="V92" t="n">
-        <v>0</v>
-      </c>
-      <c r="W92" t="n">
-        <v>0</v>
-      </c>
-      <c r="X92" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y92" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z92" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB92" t="n">
-        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.08</v>
+        <v>2.39</v>
       </c>
       <c r="M94" t="n">
-        <v>12</v>
+        <v>3.25</v>
       </c>
       <c r="N94" t="n">
-        <v>19</v>
+        <v>2.8</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12582,10 +12582,10 @@
         <v>0</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="M95" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="N95" t="n">
-        <v>3.11</v>
+        <v>3.23</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="Z95" t="n">
-        <v>2.25</v>
+        <v>2.03</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.39</v>
+        <v>1.99</v>
       </c>
       <c r="M96" t="n">
-        <v>3.25</v>
+        <v>3.39</v>
       </c>
       <c r="N96" t="n">
-        <v>2.8</v>
+        <v>3.11</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.93</v>
+        <v>2.65</v>
       </c>
       <c r="M97" t="n">
-        <v>3.41</v>
+        <v>3.17</v>
       </c>
       <c r="N97" t="n">
-        <v>3.23</v>
+        <v>2.66</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.03</v>
+        <v>1.63</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.65</v>
+        <v>1.08</v>
       </c>
       <c r="M98" t="n">
-        <v>3.17</v>
+        <v>12</v>
       </c>
       <c r="N98" t="n">
-        <v>2.66</v>
+        <v>19</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,16 +13350,16 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,16 +13866,16 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="M108" t="n">
-        <v>4.15</v>
+        <v>3.65</v>
       </c>
       <c r="N108" t="n">
-        <v>5.4</v>
+        <v>2.25</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="Z108" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="M109" t="n">
         <v>3.65</v>
       </c>
       <c r="N109" t="n">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.85</v>
+        <v>7.2</v>
       </c>
       <c r="M112" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="N112" t="n">
-        <v>4.2</v>
+        <v>1.35</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2004,10 +2004,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.17</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
-        <v>7.7</v>
+        <v>3.45</v>
       </c>
       <c r="N13" t="n">
-        <v>16</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.75</v>
+        <v>2.42</v>
       </c>
       <c r="M31" t="n">
-        <v>3.51</v>
+        <v>3.29</v>
       </c>
       <c r="N31" t="n">
-        <v>1.93</v>
+        <v>2.84</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6390,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6777,10 +6777,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="M52" t="n">
-        <v>3.34</v>
+        <v>3.53</v>
       </c>
       <c r="N52" t="n">
-        <v>3.45</v>
+        <v>3.78</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7551,10 +7551,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7674,7 +7674,7 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="Z56" t="n">
         <v>2.15</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7809,10 +7809,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.82</v>
+        <v>3.31</v>
       </c>
       <c r="M63" t="n">
-        <v>3.35</v>
+        <v>3.21</v>
       </c>
       <c r="N63" t="n">
-        <v>4.3</v>
+        <v>1.97</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.44</v>
+        <v>1.65</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N64" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8792,17 +8792,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.65</v>
+        <v>3.3</v>
       </c>
       <c r="M66" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N66" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="M67" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N67" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.68</v>
+        <v>2.44</v>
       </c>
       <c r="M70" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N70" t="n">
-        <v>4.5</v>
+        <v>2.4</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.97</v>
+        <v>1.65</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="M71" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N71" t="n">
-        <v>2.1</v>
+        <v>3.85</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9695,17 +9695,17 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="M73" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N73" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9870,7 +9870,7 @@
         <v>2.35</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11292,10 +11292,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,16 +11673,16 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.93</v>
+        <v>1.52</v>
       </c>
       <c r="M88" t="n">
-        <v>3.13</v>
+        <v>4.6</v>
       </c>
       <c r="N88" t="n">
-        <v>3.53</v>
+        <v>5.1</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,16 +11802,16 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.94</v>
+        <v>1.47</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12324,10 +12324,10 @@
         <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.39</v>
+        <v>1.08</v>
       </c>
       <c r="M94" t="n">
-        <v>3.25</v>
+        <v>12</v>
       </c>
       <c r="N94" t="n">
-        <v>2.8</v>
+        <v>19</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,16 +12576,16 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.93</v>
+        <v>2.65</v>
       </c>
       <c r="M95" t="n">
-        <v>3.41</v>
+        <v>3.17</v>
       </c>
       <c r="N95" t="n">
-        <v>3.23</v>
+        <v>2.66</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Z95" t="n">
-        <v>2.03</v>
+        <v>1.63</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="M96" t="n">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="N96" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="Z96" t="n">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.65</v>
+        <v>1.99</v>
       </c>
       <c r="M97" t="n">
-        <v>3.17</v>
+        <v>3.39</v>
       </c>
       <c r="N97" t="n">
-        <v>2.66</v>
+        <v>3.11</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.08</v>
+        <v>1.93</v>
       </c>
       <c r="M98" t="n">
-        <v>12</v>
+        <v>3.41</v>
       </c>
       <c r="N98" t="n">
-        <v>19</v>
+        <v>3.23</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="M103" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="N103" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="Z103" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>3.63</v>
+        <v>3</v>
       </c>
       <c r="M104" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="N104" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,16 +13866,16 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Z104" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AA104" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,16 +14124,16 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="M109" t="n">
-        <v>3.65</v>
+        <v>4.15</v>
       </c>
       <c r="N109" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="M110" t="n">
         <v>4.2</v>
       </c>
       <c r="N110" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Z110" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="M111" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="N111" t="n">
-        <v>2.15</v>
+        <v>1.35</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.63</v>
+        <v>2.02</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="M116" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="N116" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15420,10 +15420,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="M119" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N119" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="M121" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="N121" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="M124" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N124" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16536,14 +16536,14 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="M125" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N125" t="n">
         <v>3.25</v>
       </c>
-      <c r="N125" t="n">
-        <v>3.1</v>
-      </c>
       <c r="O125" t="n">
         <v>0</v>
       </c>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="Z125" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.17</v>
+        <v>2.15</v>
       </c>
       <c r="M12" t="n">
-        <v>7.7</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>16</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,16 +1998,16 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.15</v>
+        <v>1.17</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>7.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>16</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>CSKA Moskva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="M24" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>12.5</v>
+        <v>5.3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z24" t="n">
         <v>1.68</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.18</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.42</v>
+        <v>3.75</v>
       </c>
       <c r="M31" t="n">
-        <v>3.29</v>
+        <v>3.51</v>
       </c>
       <c r="N31" t="n">
-        <v>2.84</v>
+        <v>1.93</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.86</v>
+        <v>2.42</v>
       </c>
       <c r="M34" t="n">
-        <v>3.65</v>
+        <v>3.29</v>
       </c>
       <c r="N34" t="n">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.22</v>
+        <v>1.58</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6261,10 +6261,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7551,10 +7551,10 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7809,10 +7809,10 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="M64" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N64" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8792,17 +8792,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.3</v>
+        <v>1.62</v>
       </c>
       <c r="M66" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="N66" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9050,17 +9050,17 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="M68" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N68" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.7</v>
+        <v>2.44</v>
       </c>
       <c r="M69" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N69" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N70" t="n">
-        <v>2.4</v>
+        <v>3.85</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="Z70" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="M72" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N72" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="M73" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N73" t="n">
-        <v>3.85</v>
+        <v>2.1</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>3.8</v>
+        <v>2.33</v>
       </c>
       <c r="M78" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N78" t="n">
-        <v>1.83</v>
+        <v>2.9</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.67</v>
+        <v>2.09</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.07</v>
+        <v>1.74</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="M79" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="N79" t="n">
-        <v>2.9</v>
+        <v>5.4</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,16 +10641,16 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="M81" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="N81" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,16 +10899,16 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="M84" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="N84" t="n">
-        <v>5.4</v>
+        <v>2.6</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,16 +11286,16 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="M88" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="N88" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,16 +11802,16 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="Z88" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="M96" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N96" t="n">
-        <v>2.9</v>
+        <v>3.23</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="M97" t="n">
-        <v>3.39</v>
+        <v>3.25</v>
       </c>
       <c r="N97" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.25</v>
+        <v>1.68</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="M98" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="N98" t="n">
-        <v>3.23</v>
+        <v>3.11</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="Z98" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="M99" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="N99" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="Z99" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>3.45</v>
+        <v>3.63</v>
       </c>
       <c r="M100" t="n">
-        <v>3.35</v>
+        <v>3.68</v>
       </c>
       <c r="N100" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,16 +13350,16 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="Z100" t="n">
-        <v>1.63</v>
+        <v>2.17</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="M103" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="N103" t="n">
-        <v>5.6</v>
+        <v>2.25</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,7 +13737,7 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Z103" t="n">
         <v>2.1</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,16 +14124,16 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.45</v>
+        <v>3.45</v>
       </c>
       <c r="M110" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="N110" t="n">
-        <v>6.2</v>
+        <v>2.15</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="Z110" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>7.2</v>
+        <v>1.85</v>
       </c>
       <c r="M111" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="N111" t="n">
-        <v>1.35</v>
+        <v>4.2</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="Z111" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK125"/>
+  <dimension ref="A1:AK126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.45</v>
+        <v>2.54</v>
       </c>
       <c r="M2" t="n">
-        <v>3.55</v>
+        <v>3.28</v>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1746,10 +1746,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>3.27</v>
       </c>
       <c r="N11" t="n">
-        <v>4.15</v>
+        <v>2.93</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.17</v>
+        <v>1.85</v>
       </c>
       <c r="M13" t="n">
-        <v>7.7</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>16</v>
+        <v>3.51</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,16 +2127,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>BFC Daugavpils</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="M29" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>3.26</v>
+        <v>3.45</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.35</v>
+        <v>1.66</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.6</v>
+        <v>2.22</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.75</v>
+        <v>2.06</v>
       </c>
       <c r="M31" t="n">
-        <v>3.51</v>
+        <v>3.05</v>
       </c>
       <c r="N31" t="n">
-        <v>1.93</v>
+        <v>3.26</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4971,10 +4971,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5272,27 +5272,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45926.52083333334</v>
+        <v>45926.5</v>
       </c>
     </row>
     <row r="39">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N40" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5788,27 +5788,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45926.52430555555</v>
+        <v>45926.52083333334</v>
       </c>
     </row>
     <row r="43">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45926.52777777778</v>
+        <v>45926.52430555555</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45926.54166666666</v>
+        <v>45926.52777777778</v>
       </c>
     </row>
     <row r="45">
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.34</v>
+        <v>2.1</v>
       </c>
       <c r="M45" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="N45" t="n">
-        <v>5.7</v>
+        <v>2.85</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6261,10 +6261,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.43</v>
+        <v>1.27</v>
       </c>
       <c r="M49" t="n">
-        <v>3.81</v>
+        <v>5.2</v>
       </c>
       <c r="N49" t="n">
-        <v>2.24</v>
+        <v>8</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6777,10 +6777,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.57</v>
+        <v>1.89</v>
       </c>
       <c r="M50" t="n">
-        <v>3.93</v>
+        <v>3.34</v>
       </c>
       <c r="N50" t="n">
-        <v>4.33</v>
+        <v>3.45</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="M51" t="n">
-        <v>3.34</v>
+        <v>3.93</v>
       </c>
       <c r="N51" t="n">
-        <v>3.45</v>
+        <v>4.33</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7422,10 +7422,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45926.55208333334</v>
+        <v>45926.54166666666</v>
       </c>
     </row>
     <row r="55">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>45926.5625</v>
+        <v>45926.55208333334</v>
       </c>
     </row>
     <row r="56">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="M57" t="n">
-        <v>3.75</v>
+        <v>3.97</v>
       </c>
       <c r="N57" t="n">
-        <v>4.4</v>
+        <v>3.32</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,16 +7803,16 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
         <v>0</v>
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45926.58333333334</v>
+        <v>45926.5625</v>
       </c>
     </row>
     <row r="59">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.82</v>
+        <v>3.31</v>
       </c>
       <c r="M59" t="n">
-        <v>3.35</v>
+        <v>3.21</v>
       </c>
       <c r="N59" t="n">
-        <v>4.3</v>
+        <v>1.97</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8626,12 +8626,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45926.60416666666</v>
+        <v>45926.58333333334</v>
       </c>
     </row>
     <row r="65">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="M65" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N65" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.62</v>
+        <v>2.44</v>
       </c>
       <c r="M66" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N66" t="n">
-        <v>5.3</v>
+        <v>2.4</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.12</v>
+        <v>1.65</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9050,17 +9050,17 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.65</v>
+        <v>3.3</v>
       </c>
       <c r="M68" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N68" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.44</v>
+        <v>1.68</v>
       </c>
       <c r="M69" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N69" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="Z69" t="n">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="M70" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="N70" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,10 +9570,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="M71" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N71" t="n">
         <v>3.85</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9695,17 +9695,17 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>3.3</v>
+        <v>1.65</v>
       </c>
       <c r="M73" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="N73" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45926.625</v>
+        <v>45926.60416666666</v>
       </c>
     </row>
     <row r="75">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="M77" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N77" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="M79" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="N79" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,16 +10641,16 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,16 +10899,16 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11034,10 +11034,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,16 +11931,16 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA89" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB89" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12367,12 +12367,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="M93" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="N93" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Z93" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45926.63541666666</v>
+        <v>45926.625</v>
       </c>
     </row>
     <row r="94">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.08</v>
+        <v>3.75</v>
       </c>
       <c r="M94" t="n">
-        <v>12</v>
+        <v>3.56</v>
       </c>
       <c r="N94" t="n">
-        <v>19</v>
+        <v>1.75</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,16 +12576,16 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.18</v>
+        <v>1.68</v>
       </c>
       <c r="Z94" t="n">
-        <v>4.75</v>
+        <v>2.05</v>
       </c>
       <c r="AA94" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB94" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="n">
         <v>0</v>
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45926.64583333334</v>
+        <v>45926.63541666666</v>
       </c>
     </row>
     <row r="95">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.65</v>
+        <v>1.99</v>
       </c>
       <c r="M95" t="n">
-        <v>3.17</v>
+        <v>3.39</v>
       </c>
       <c r="N95" t="n">
-        <v>2.66</v>
+        <v>3.11</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.93</v>
+        <v>3.02</v>
       </c>
       <c r="M96" t="n">
-        <v>3.41</v>
+        <v>3.12</v>
       </c>
       <c r="N96" t="n">
-        <v>3.23</v>
+        <v>2.39</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="Z96" t="n">
-        <v>2.03</v>
+        <v>1.68</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="M97" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="N97" t="n">
-        <v>2.9</v>
+        <v>3.23</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.99</v>
+        <v>1.08</v>
       </c>
       <c r="M98" t="n">
-        <v>3.39</v>
+        <v>12</v>
       </c>
       <c r="N98" t="n">
-        <v>3.11</v>
+        <v>19</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="Z98" t="n">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13141,27 +13141,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.55</v>
+        <v>2.65</v>
       </c>
       <c r="M99" t="n">
-        <v>4.2</v>
+        <v>3.17</v>
       </c>
       <c r="N99" t="n">
-        <v>5.6</v>
+        <v>2.66</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="Z99" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45926.65625</v>
+        <v>45926.64583333334</v>
       </c>
     </row>
     <row r="100">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,16 +13350,16 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="M102" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="N102" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="Z102" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>3</v>
+        <v>1.45</v>
       </c>
       <c r="M103" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="N103" t="n">
-        <v>2.25</v>
+        <v>6.2</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13740,7 +13740,7 @@
         <v>1.72</v>
       </c>
       <c r="Z103" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>7.2</v>
+        <v>3.63</v>
       </c>
       <c r="M105" t="n">
-        <v>4.8</v>
+        <v>3.68</v>
       </c>
       <c r="N105" t="n">
-        <v>1.35</v>
+        <v>1.91</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13998,13 +13998,13 @@
         <v>1.7</v>
       </c>
       <c r="Z105" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>3.45</v>
+        <v>1.85</v>
       </c>
       <c r="M110" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N110" t="n">
-        <v>2.15</v>
+        <v>4.2</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.85</v>
+        <v>3.45</v>
       </c>
       <c r="M111" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N111" t="n">
-        <v>4.2</v>
+        <v>2.15</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.82</v>
+        <v>1.63</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45926.66666666666</v>
+        <v>45926.65625</v>
       </c>
     </row>
     <row r="114">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15334,12 +15334,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15420,10 +15420,10 @@
         <v>0</v>
       </c>
       <c r="AA116" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AK116" s="3" t="n">
-        <v>45926.67708333334</v>
+        <v>45926.66666666666</v>
       </c>
     </row>
     <row r="117">
@@ -15463,12 +15463,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15549,10 +15549,10 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB117" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -15583,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="AK117" s="3" t="n">
-        <v>45926.6875</v>
+        <v>45926.67708333334</v>
       </c>
     </row>
     <row r="118">
@@ -15592,27 +15592,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15712,7 +15712,7 @@
         <v>0</v>
       </c>
       <c r="AK118" s="3" t="n">
-        <v>45926.79166666666</v>
+        <v>45926.6875</v>
       </c>
     </row>
     <row r="119">
@@ -15721,12 +15721,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AK119" s="3" t="n">
-        <v>45926.83333333334</v>
+        <v>45926.79166666666</v>
       </c>
     </row>
     <row r="120">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45926.875</v>
+        <v>45926.83333333334</v>
       </c>
     </row>
     <row r="122">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16237,12 +16237,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45926.89583333334</v>
+        <v>45926.875</v>
       </c>
     </row>
     <row r="124">
@@ -16366,12 +16366,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="AK124" s="3" t="n">
-        <v>45926.91666666666</v>
+        <v>45926.89583333334</v>
       </c>
     </row>
     <row r="125">
@@ -16495,126 +16495,255 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M125" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N125" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK125" s="3" t="n">
+        <v>45926.91666666666</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
+      <c r="E126" t="inlineStr">
         <is>
           <t>San Diego Wave</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>Orlando Pride</t>
         </is>
       </c>
-      <c r="G125" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" t="inlineStr">
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L125" t="n">
+      <c r="L126" t="n">
         <v>2.08</v>
       </c>
-      <c r="M125" t="n">
+      <c r="M126" t="n">
         <v>3.4</v>
       </c>
-      <c r="N125" t="n">
+      <c r="N126" t="n">
         <v>3.25</v>
       </c>
-      <c r="O125" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" t="n">
-        <v>0</v>
-      </c>
-      <c r="T125" t="n">
-        <v>0</v>
-      </c>
-      <c r="U125" t="n">
-        <v>0</v>
-      </c>
-      <c r="V125" t="n">
-        <v>0</v>
-      </c>
-      <c r="W125" t="n">
-        <v>0</v>
-      </c>
-      <c r="X125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y125" t="n">
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
         <v>1.9</v>
       </c>
-      <c r="Z125" t="n">
+      <c r="Z126" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK125" s="3" t="n">
+      <c r="AA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK126" s="3" t="n">
         <v>45926.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK126"/>
+  <dimension ref="A1:AK121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.84</v>
+        <v>3.35</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N6" t="n">
-        <v>3.55</v>
+        <v>2.01</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.35</v>
+        <v>1.84</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2.01</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="N13" t="n">
-        <v>3.51</v>
+        <v>2.93</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CSKA Moskva</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3595,12 +3595,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3715,7 +3715,7 @@
         <v>0</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>45926.45833333334</v>
+        <v>45926.47916666666</v>
       </c>
     </row>
     <row r="26">
@@ -3724,27 +3724,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3844,7 +3844,7 @@
         <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>45926.45833333334</v>
+        <v>45926.5</v>
       </c>
     </row>
     <row r="27">
@@ -3853,27 +3853,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>45926.47916666666</v>
+        <v>45926.5</v>
       </c>
     </row>
     <row r="28">
@@ -3982,27 +3982,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BFC Daugavpils</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
         <v>0</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>45926.47916666666</v>
+        <v>45926.5</v>
       </c>
     </row>
     <row r="29">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.86</v>
+        <v>3.75</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>3.51</v>
       </c>
       <c r="N29" t="n">
-        <v>3.45</v>
+        <v>1.93</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.22</v>
+        <v>1.82</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4584,10 +4584,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4756,27 +4756,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45926.5</v>
+        <v>45926.52083333334</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="M35" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="N35" t="n">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,16 +4965,16 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45926.5</v>
+        <v>45926.52083333334</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45926.5</v>
+        <v>45926.52083333334</v>
       </c>
     </row>
     <row r="37">
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45926.5</v>
+        <v>45926.52083333334</v>
       </c>
     </row>
     <row r="38">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>45926.5</v>
+        <v>45926.52430555555</v>
       </c>
     </row>
     <row r="39">
@@ -5401,12 +5401,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Dhamk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5521,7 +5521,7 @@
         <v>0</v>
       </c>
       <c r="AK39" s="3" t="n">
-        <v>45926.52083333334</v>
+        <v>45926.52777777778</v>
       </c>
     </row>
     <row r="40">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="M40" t="n">
-        <v>3.55</v>
+        <v>3.81</v>
       </c>
       <c r="N40" t="n">
-        <v>3.65</v>
+        <v>2.24</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45926.52083333334</v>
+        <v>45926.54166666666</v>
       </c>
     </row>
     <row r="41">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45926.52083333334</v>
+        <v>45926.54166666666</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5874,10 +5874,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45926.52083333334</v>
+        <v>45926.54166666666</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6003,10 +6003,10 @@
         <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45926.52430555555</v>
+        <v>45926.54166666666</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dhamk</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45926.52777777778</v>
+        <v>45926.54166666666</v>
       </c>
     </row>
     <row r="45">
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6261,10 +6261,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.09</v>
+        <v>1.27</v>
       </c>
       <c r="M47" t="n">
-        <v>3.47</v>
+        <v>5.2</v>
       </c>
       <c r="N47" t="n">
-        <v>2.83</v>
+        <v>8</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.27</v>
+        <v>1.75</v>
       </c>
       <c r="M49" t="n">
-        <v>5.2</v>
+        <v>3.53</v>
       </c>
       <c r="N49" t="n">
-        <v>8</v>
+        <v>3.78</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6820,12 +6820,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45926.54166666666</v>
+        <v>45926.55208333334</v>
       </c>
     </row>
     <row r="51">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,49 +6990,49 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
         <v>1.57</v>
       </c>
-      <c r="M51" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="N51" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.6</v>
-      </c>
       <c r="Z51" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="AK51" s="3" t="n">
-        <v>45926.54166666666</v>
+        <v>45926.5625</v>
       </c>
     </row>
     <row r="52">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7198,7 +7198,7 @@
         <v>0</v>
       </c>
       <c r="AK52" s="3" t="n">
-        <v>45926.54166666666</v>
+        <v>45926.5625</v>
       </c>
     </row>
     <row r="53">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.34</v>
+        <v>1.74</v>
       </c>
       <c r="M53" t="n">
-        <v>5.1</v>
+        <v>3.75</v>
       </c>
       <c r="N53" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7293,10 +7293,10 @@
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="3" t="n">
-        <v>45926.54166666666</v>
+        <v>45926.5625</v>
       </c>
     </row>
     <row r="54">
@@ -7336,12 +7336,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="M54" t="n">
-        <v>3.81</v>
+        <v>3.15</v>
       </c>
       <c r="N54" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,16 +7416,16 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AK54" s="3" t="n">
-        <v>45926.54166666666</v>
+        <v>45926.58333333334</v>
       </c>
     </row>
     <row r="55">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="AK55" s="3" t="n">
-        <v>45926.55208333334</v>
+        <v>45926.58333333334</v>
       </c>
     </row>
     <row r="56">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7714,7 +7714,7 @@
         <v>0</v>
       </c>
       <c r="AK56" s="3" t="n">
-        <v>45926.5625</v>
+        <v>45926.58333333334</v>
       </c>
     </row>
     <row r="57">
@@ -7723,12 +7723,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7843,7 +7843,7 @@
         <v>0</v>
       </c>
       <c r="AK57" s="3" t="n">
-        <v>45926.5625</v>
+        <v>45926.58333333334</v>
       </c>
     </row>
     <row r="58">
@@ -7852,12 +7852,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7972,7 +7972,7 @@
         <v>0</v>
       </c>
       <c r="AK58" s="3" t="n">
-        <v>45926.5625</v>
+        <v>45926.58333333334</v>
       </c>
     </row>
     <row r="59">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45926.58333333334</v>
+        <v>45926.60416666666</v>
       </c>
     </row>
     <row r="61">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>2.75</v>
+        <v>1.68</v>
       </c>
       <c r="M61" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="N61" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45926.58333333334</v>
+        <v>45926.60416666666</v>
       </c>
     </row>
     <row r="62">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="M62" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N62" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45926.58333333334</v>
+        <v>45926.60416666666</v>
       </c>
     </row>
     <row r="63">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45926.58333333334</v>
+        <v>45926.60416666666</v>
       </c>
     </row>
     <row r="64">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45926.58333333334</v>
+        <v>45926.60416666666</v>
       </c>
     </row>
     <row r="65">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="M65" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N65" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="M66" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N66" t="n">
-        <v>2.4</v>
+        <v>3.85</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="Z66" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="M67" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N67" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9179,17 +9179,17 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,49 +9312,49 @@
         </is>
       </c>
       <c r="L69" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M69" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N69" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z69" t="n">
         <v>1.68</v>
-      </c>
-      <c r="M69" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N69" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0</v>
-      </c>
-      <c r="S69" t="n">
-        <v>0</v>
-      </c>
-      <c r="T69" t="n">
-        <v>0</v>
-      </c>
-      <c r="U69" t="n">
-        <v>0</v>
-      </c>
-      <c r="V69" t="n">
-        <v>0</v>
-      </c>
-      <c r="W69" t="n">
-        <v>0</v>
-      </c>
-      <c r="X69" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>1.52</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9400,12 +9400,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9520,7 +9520,7 @@
         <v>0</v>
       </c>
       <c r="AK70" s="3" t="n">
-        <v>45926.60416666666</v>
+        <v>45926.625</v>
       </c>
     </row>
     <row r="71">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45926.60416666666</v>
+        <v>45926.625</v>
       </c>
     </row>
     <row r="72">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9695,7 +9695,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45926.60416666666</v>
+        <v>45926.625</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.65</v>
+        <v>2.7</v>
       </c>
       <c r="M73" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N73" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45926.60416666666</v>
+        <v>45926.625</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45926.60416666666</v>
+        <v>45926.625</v>
       </c>
     </row>
     <row r="75">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="M79" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="N79" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,16 +10899,16 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.63</v>
+        <v>2.33</v>
       </c>
       <c r="M82" t="n">
-        <v>3.69</v>
+        <v>3.25</v>
       </c>
       <c r="N82" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,16 +11028,16 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11292,10 +11292,10 @@
         <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="M86" t="n">
-        <v>3.13</v>
+        <v>3.75</v>
       </c>
       <c r="N86" t="n">
-        <v>3.53</v>
+        <v>4.2</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.52</v>
+        <v>3.75</v>
       </c>
       <c r="M89" t="n">
-        <v>4.6</v>
+        <v>3.56</v>
       </c>
       <c r="N89" t="n">
-        <v>5.1</v>
+        <v>1.75</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,16 +11931,16 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="Z89" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AA89" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB89" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC89" t="n">
         <v>0</v>
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>45926.625</v>
+        <v>45926.63541666666</v>
       </c>
     </row>
     <row r="90">
@@ -11980,12 +11980,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12100,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>45926.625</v>
+        <v>45926.64583333334</v>
       </c>
     </row>
     <row r="91">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,16 +12189,16 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45926.625</v>
+        <v>45926.64583333334</v>
       </c>
     </row>
     <row r="92">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.6</v>
+        <v>3.02</v>
       </c>
       <c r="M92" t="n">
-        <v>4.1</v>
+        <v>3.12</v>
       </c>
       <c r="N92" t="n">
-        <v>5.6</v>
+        <v>2.39</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45926.625</v>
+        <v>45926.64583333334</v>
       </c>
     </row>
     <row r="93">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.8</v>
+        <v>1.93</v>
       </c>
       <c r="M93" t="n">
-        <v>3.7</v>
+        <v>3.41</v>
       </c>
       <c r="N93" t="n">
-        <v>1.83</v>
+        <v>3.23</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="Z93" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12487,7 +12487,7 @@
         <v>0</v>
       </c>
       <c r="AK93" s="3" t="n">
-        <v>45926.625</v>
+        <v>45926.64583333334</v>
       </c>
     </row>
     <row r="94">
@@ -12496,12 +12496,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>3.75</v>
+        <v>1.99</v>
       </c>
       <c r="M94" t="n">
-        <v>3.56</v>
+        <v>3.39</v>
       </c>
       <c r="N94" t="n">
-        <v>1.75</v>
+        <v>3.11</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="Z94" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="AK94" s="3" t="n">
-        <v>45926.63541666666</v>
+        <v>45926.64583333334</v>
       </c>
     </row>
     <row r="95">
@@ -12625,12 +12625,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.99</v>
+        <v>6.5</v>
       </c>
       <c r="M95" t="n">
-        <v>3.39</v>
+        <v>4.1</v>
       </c>
       <c r="N95" t="n">
-        <v>3.11</v>
+        <v>1.42</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="Z95" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12745,7 +12745,7 @@
         <v>0</v>
       </c>
       <c r="AK95" s="3" t="n">
-        <v>45926.64583333334</v>
+        <v>45926.65625</v>
       </c>
     </row>
     <row r="96">
@@ -12754,27 +12754,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.02</v>
+        <v>1.58</v>
       </c>
       <c r="M96" t="n">
-        <v>3.12</v>
+        <v>3.95</v>
       </c>
       <c r="N96" t="n">
-        <v>2.39</v>
+        <v>5.1</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="AK96" s="3" t="n">
-        <v>45926.64583333334</v>
+        <v>45926.65625</v>
       </c>
     </row>
     <row r="97">
@@ -12883,27 +12883,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.93</v>
+        <v>3.45</v>
       </c>
       <c r="M97" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="N97" t="n">
-        <v>3.23</v>
+        <v>2.15</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.03</v>
+        <v>1.63</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45926.64583333334</v>
+        <v>45926.65625</v>
       </c>
     </row>
     <row r="98">
@@ -13012,27 +13012,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.08</v>
+        <v>1.85</v>
       </c>
       <c r="M98" t="n">
-        <v>12</v>
+        <v>3.65</v>
       </c>
       <c r="N98" t="n">
-        <v>19</v>
+        <v>4.2</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,16 +13092,16 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.18</v>
+        <v>1.98</v>
       </c>
       <c r="Z98" t="n">
-        <v>4.75</v>
+        <v>1.82</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
         <v>0</v>
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45926.64583333334</v>
+        <v>45926.65625</v>
       </c>
     </row>
     <row r="99">
@@ -13141,27 +13141,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,14 +13182,14 @@
         </is>
       </c>
       <c r="L99" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M99" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N99" t="n">
         <v>2.65</v>
       </c>
-      <c r="M99" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="N99" t="n">
-        <v>2.66</v>
-      </c>
       <c r="O99" t="n">
         <v>0</v>
       </c>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45926.64583333334</v>
+        <v>45926.65625</v>
       </c>
     </row>
     <row r="100">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="M101" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="N101" t="n">
-        <v>2.25</v>
+        <v>1.35</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Z101" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>1.55</v>
+        <v>3.63</v>
       </c>
       <c r="M102" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="N102" t="n">
-        <v>5.6</v>
+        <v>1.91</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,16 +13608,16 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="Z102" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="M103" t="n">
         <v>4.2</v>
       </c>
       <c r="N103" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Z103" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,10 +13827,10 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M104" t="n">
-        <v>4.1</v>
+        <v>3.53</v>
       </c>
       <c r="N104" t="n">
         <v>4.8</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="Z104" t="n">
-        <v>2.25</v>
+        <v>1.79</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3.63</v>
+        <v>3</v>
       </c>
       <c r="M105" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="N105" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,16 +13995,16 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Z105" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AA105" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB105" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="M107" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="N107" t="n">
-        <v>1.42</v>
+        <v>2.45</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14431,12 +14431,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="AK109" s="3" t="n">
-        <v>45926.65625</v>
+        <v>45926.66666666666</v>
       </c>
     </row>
     <row r="110">
@@ -14560,27 +14560,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14680,7 +14680,7 @@
         <v>0</v>
       </c>
       <c r="AK110" s="3" t="n">
-        <v>45926.65625</v>
+        <v>45926.66666666666</v>
       </c>
     </row>
     <row r="111">
@@ -14689,12 +14689,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14809,7 +14809,7 @@
         <v>0</v>
       </c>
       <c r="AK111" s="3" t="n">
-        <v>45926.65625</v>
+        <v>45926.66666666666</v>
       </c>
     </row>
     <row r="112">
@@ -14818,27 +14818,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,56 +14859,56 @@
         </is>
       </c>
       <c r="L112" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="M112" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="N112" t="n">
+        <v>28</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>0</v>
+      </c>
+      <c r="U112" t="n">
+        <v>0</v>
+      </c>
+      <c r="V112" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB112" t="n">
         <v>1.6</v>
       </c>
-      <c r="M112" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="N112" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="P112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
-      <c r="R112" t="n">
-        <v>0</v>
-      </c>
-      <c r="S112" t="n">
-        <v>0</v>
-      </c>
-      <c r="T112" t="n">
-        <v>0</v>
-      </c>
-      <c r="U112" t="n">
-        <v>0</v>
-      </c>
-      <c r="V112" t="n">
-        <v>0</v>
-      </c>
-      <c r="W112" t="n">
-        <v>0</v>
-      </c>
-      <c r="X112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y112" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z112" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA112" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB112" t="n">
-        <v>0</v>
-      </c>
       <c r="AC112" t="n">
         <v>0</v>
       </c>
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45926.65625</v>
+        <v>45926.67708333334</v>
       </c>
     </row>
     <row r="113">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45926.65625</v>
+        <v>45926.6875</v>
       </c>
     </row>
     <row r="114">
@@ -15076,27 +15076,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45926.66666666666</v>
+        <v>45926.79166666666</v>
       </c>
     </row>
     <row r="115">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45926.66666666666</v>
+        <v>45926.83333333334</v>
       </c>
     </row>
     <row r="116">
@@ -15334,27 +15334,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AK116" s="3" t="n">
-        <v>45926.66666666666</v>
+        <v>45926.83333333334</v>
       </c>
     </row>
     <row r="117">
@@ -15463,27 +15463,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="M117" t="n">
-        <v>8.5</v>
+        <v>3.55</v>
       </c>
       <c r="N117" t="n">
-        <v>28</v>
+        <v>3.9</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,16 +15543,16 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA117" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -15583,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="AK117" s="3" t="n">
-        <v>45926.67708333334</v>
+        <v>45926.875</v>
       </c>
     </row>
     <row r="118">
@@ -15592,27 +15592,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15712,7 +15712,7 @@
         <v>0</v>
       </c>
       <c r="AK118" s="3" t="n">
-        <v>45926.6875</v>
+        <v>45926.875</v>
       </c>
     </row>
     <row r="119">
@@ -15721,12 +15721,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AK119" s="3" t="n">
-        <v>45926.79166666666</v>
+        <v>45926.89583333334</v>
       </c>
     </row>
     <row r="120">
@@ -15850,7 +15850,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="M120" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="N120" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45926.83333333334</v>
+        <v>45926.91666666666</v>
       </c>
     </row>
     <row r="121">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16099,651 +16099,6 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45926.83333333334</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="n">
-        <v>45926</v>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>Gotham FC</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Portland Thorns</t>
-        </is>
-      </c>
-      <c r="G122" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" t="n">
-        <v>0</v>
-      </c>
-      <c r="J122" t="n">
-        <v>0</v>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L122" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="M122" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N122" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="P122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" t="n">
-        <v>0</v>
-      </c>
-      <c r="U122" t="n">
-        <v>0</v>
-      </c>
-      <c r="V122" t="n">
-        <v>0</v>
-      </c>
-      <c r="W122" t="n">
-        <v>0</v>
-      </c>
-      <c r="X122" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y122" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Z122" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ122" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK122" s="3" t="n">
-        <v>45926.875</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="n">
-        <v>45926</v>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Kansas City</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Chicago Red Stars</t>
-        </is>
-      </c>
-      <c r="G123" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L123" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M123" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N123" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O123" t="n">
-        <v>0</v>
-      </c>
-      <c r="P123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" t="n">
-        <v>0</v>
-      </c>
-      <c r="T123" t="n">
-        <v>0</v>
-      </c>
-      <c r="U123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" t="n">
-        <v>0</v>
-      </c>
-      <c r="W123" t="n">
-        <v>0</v>
-      </c>
-      <c r="X123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y123" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z123" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK123" s="3" t="n">
-        <v>45926.875</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="n">
-        <v>45926</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Austin II</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>Portland Timbers II</t>
-        </is>
-      </c>
-      <c r="G124" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L124" t="n">
-        <v>0</v>
-      </c>
-      <c r="M124" t="n">
-        <v>0</v>
-      </c>
-      <c r="N124" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
-      <c r="R124" t="n">
-        <v>0</v>
-      </c>
-      <c r="S124" t="n">
-        <v>0</v>
-      </c>
-      <c r="T124" t="n">
-        <v>0</v>
-      </c>
-      <c r="U124" t="n">
-        <v>0</v>
-      </c>
-      <c r="V124" t="n">
-        <v>0</v>
-      </c>
-      <c r="W124" t="n">
-        <v>0</v>
-      </c>
-      <c r="X124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK124" s="3" t="n">
-        <v>45926.89583333334</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="n">
-        <v>45926</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>El Paso Locomotive</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Rhode Island</t>
-        </is>
-      </c>
-      <c r="G125" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L125" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="M125" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N125" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O125" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0</v>
-      </c>
-      <c r="S125" t="n">
-        <v>0</v>
-      </c>
-      <c r="T125" t="n">
-        <v>0</v>
-      </c>
-      <c r="U125" t="n">
-        <v>0</v>
-      </c>
-      <c r="V125" t="n">
-        <v>0</v>
-      </c>
-      <c r="W125" t="n">
-        <v>0</v>
-      </c>
-      <c r="X125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y125" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z125" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK125" s="3" t="n">
-        <v>45926.91666666666</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="n">
-        <v>45926</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>23:30</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Orlando Pride</t>
-        </is>
-      </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L126" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="M126" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N126" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="P126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
-      </c>
-      <c r="S126" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" t="n">
-        <v>0</v>
-      </c>
-      <c r="U126" t="n">
-        <v>0</v>
-      </c>
-      <c r="V126" t="n">
-        <v>0</v>
-      </c>
-      <c r="W126" t="n">
-        <v>0</v>
-      </c>
-      <c r="X126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y126" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z126" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK126" s="3" t="n">
         <v>45926.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK121"/>
+  <dimension ref="A1:AK122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,52 +678,52 @@
         <v>2.38</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="M6" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dewa United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dewa United</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="N12" t="n">
-        <v>3.51</v>
+        <v>2.93</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ulinzi Stars</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kariobangi Sharks</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>Ulinzi Stars</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Kariobangi Sharks</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="N27" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4191,10 +4191,10 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.43</v>
+        <v>2.1</v>
       </c>
       <c r="M40" t="n">
-        <v>3.81</v>
+        <v>3.95</v>
       </c>
       <c r="N40" t="n">
-        <v>2.24</v>
+        <v>2.85</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5616,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.89</v>
+        <v>1.27</v>
       </c>
       <c r="M41" t="n">
-        <v>3.34</v>
+        <v>5.2</v>
       </c>
       <c r="N41" t="n">
-        <v>3.45</v>
+        <v>8</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="M42" t="n">
-        <v>3.95</v>
+        <v>3.34</v>
       </c>
       <c r="N42" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.34</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>5.1</v>
+        <v>3.53</v>
       </c>
       <c r="N43" t="n">
-        <v>5.7</v>
+        <v>3.78</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.09</v>
+        <v>2.43</v>
       </c>
       <c r="M44" t="n">
-        <v>3.47</v>
+        <v>3.81</v>
       </c>
       <c r="N44" t="n">
-        <v>2.83</v>
+        <v>2.24</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="M47" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="N47" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="M53" t="n">
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="N53" t="n">
-        <v>4.4</v>
+        <v>3.33</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA53" t="n">
         <v>2.15</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="M60" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N60" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8276,17 +8276,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,49 +8409,49 @@
         </is>
       </c>
       <c r="L62" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="M62" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N62" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="n">
         <v>1.65</v>
       </c>
-      <c r="M62" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N62" t="n">
-        <v>5</v>
-      </c>
-      <c r="O62" t="n">
-        <v>0</v>
-      </c>
-      <c r="P62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" t="n">
-        <v>0</v>
-      </c>
-      <c r="U62" t="n">
-        <v>0</v>
-      </c>
-      <c r="V62" t="n">
-        <v>0</v>
-      </c>
-      <c r="W62" t="n">
-        <v>0</v>
-      </c>
-      <c r="X62" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y62" t="n">
-        <v>2.02</v>
-      </c>
       <c r="Z62" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.44</v>
+        <v>1.83</v>
       </c>
       <c r="M63" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N63" t="n">
-        <v>2.4</v>
+        <v>3.85</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="M64" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N64" t="n">
-        <v>3.85</v>
+        <v>2.1</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="M66" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N66" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,49 +9054,49 @@
         </is>
       </c>
       <c r="L67" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M67" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N67" t="n">
+        <v>5</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" t="n">
+        <v>0</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z67" t="n">
         <v>1.7</v>
-      </c>
-      <c r="M67" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N67" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O67" t="n">
-        <v>0</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0</v>
-      </c>
-      <c r="S67" t="n">
-        <v>0</v>
-      </c>
-      <c r="T67" t="n">
-        <v>0</v>
-      </c>
-      <c r="U67" t="n">
-        <v>0</v>
-      </c>
-      <c r="V67" t="n">
-        <v>0</v>
-      </c>
-      <c r="W67" t="n">
-        <v>0</v>
-      </c>
-      <c r="X67" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y67" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Z67" t="n">
-        <v>1.67</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9179,17 +9179,17 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="M69" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N69" t="n">
-        <v>2.1</v>
+        <v>3.85</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="M73" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="N73" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,55 +10602,55 @@
         </is>
       </c>
       <c r="L79" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="M79" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="N79" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>0</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" t="n">
+        <v>0</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB79" t="n">
         <v>1.6</v>
-      </c>
-      <c r="M79" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N79" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" t="n">
-        <v>0</v>
-      </c>
-      <c r="S79" t="n">
-        <v>0</v>
-      </c>
-      <c r="T79" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" t="n">
-        <v>0</v>
-      </c>
-      <c r="V79" t="n">
-        <v>0</v>
-      </c>
-      <c r="W79" t="n">
-        <v>0</v>
-      </c>
-      <c r="X79" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.52</v>
+        <v>2.7</v>
       </c>
       <c r="M81" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="N81" t="n">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,16 +10899,16 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="M84" t="n">
-        <v>3.69</v>
+        <v>4.6</v>
       </c>
       <c r="N84" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,16 +11286,16 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.8</v>
+        <v>3.8</v>
       </c>
       <c r="M86" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N86" t="n">
-        <v>4.2</v>
+        <v>1.83</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.65</v>
+        <v>1.99</v>
       </c>
       <c r="M90" t="n">
-        <v>3.17</v>
+        <v>3.39</v>
       </c>
       <c r="N90" t="n">
-        <v>2.66</v>
+        <v>3.11</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.08</v>
+        <v>3.02</v>
       </c>
       <c r="M91" t="n">
-        <v>12</v>
+        <v>3.12</v>
       </c>
       <c r="N91" t="n">
-        <v>19</v>
+        <v>2.39</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,16 +12189,16 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.18</v>
+        <v>2.2</v>
       </c>
       <c r="Z91" t="n">
-        <v>4.75</v>
+        <v>1.68</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>3.02</v>
+        <v>1.93</v>
       </c>
       <c r="M92" t="n">
-        <v>3.12</v>
+        <v>3.41</v>
       </c>
       <c r="N92" t="n">
-        <v>2.39</v>
+        <v>3.23</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.93</v>
+        <v>1.08</v>
       </c>
       <c r="M93" t="n">
-        <v>3.41</v>
+        <v>12</v>
       </c>
       <c r="N93" t="n">
-        <v>3.23</v>
+        <v>19</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,16 +12447,16 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.78</v>
+        <v>1.18</v>
       </c>
       <c r="Z93" t="n">
-        <v>2.03</v>
+        <v>4.75</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.99</v>
+        <v>2.65</v>
       </c>
       <c r="M94" t="n">
-        <v>3.39</v>
+        <v>3.17</v>
       </c>
       <c r="N94" t="n">
-        <v>3.11</v>
+        <v>2.66</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="Z94" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="M95" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N95" t="n">
-        <v>1.42</v>
+        <v>2.65</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.58</v>
+        <v>3</v>
       </c>
       <c r="M96" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N96" t="n">
-        <v>5.1</v>
+        <v>2.25</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>3.45</v>
+        <v>1.58</v>
       </c>
       <c r="M97" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="N97" t="n">
-        <v>2.15</v>
+        <v>5.1</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.85</v>
+        <v>7.2</v>
       </c>
       <c r="M98" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="N98" t="n">
-        <v>4.2</v>
+        <v>1.35</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.4</v>
+        <v>1.59</v>
       </c>
       <c r="M99" t="n">
-        <v>3.45</v>
+        <v>3.53</v>
       </c>
       <c r="N99" t="n">
-        <v>2.65</v>
+        <v>4.8</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>7.2</v>
+        <v>2.5</v>
       </c>
       <c r="M101" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="N101" t="n">
-        <v>1.35</v>
+        <v>2.45</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="Z101" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>3.63</v>
+        <v>6.5</v>
       </c>
       <c r="M102" t="n">
-        <v>3.68</v>
+        <v>4.1</v>
       </c>
       <c r="N102" t="n">
-        <v>1.91</v>
+        <v>1.42</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,16 +13608,16 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Z102" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AA102" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,49 +13698,49 @@
         </is>
       </c>
       <c r="L103" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M103" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="N103" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" t="n">
         <v>1.55</v>
       </c>
-      <c r="M103" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N103" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="P103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
-      <c r="R103" t="n">
-        <v>0</v>
-      </c>
-      <c r="S103" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" t="n">
-        <v>0</v>
-      </c>
-      <c r="U103" t="n">
-        <v>0</v>
-      </c>
-      <c r="V103" t="n">
-        <v>0</v>
-      </c>
-      <c r="W103" t="n">
-        <v>0</v>
-      </c>
-      <c r="X103" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y103" t="n">
-        <v>1.75</v>
-      </c>
       <c r="Z103" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M104" t="n">
-        <v>3.53</v>
+        <v>4.15</v>
       </c>
       <c r="N104" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="M105" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="N105" t="n">
-        <v>2.25</v>
+        <v>5.6</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,7 +13995,7 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Z105" t="n">
         <v>2.1</v>
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.6</v>
+        <v>3.45</v>
       </c>
       <c r="M106" t="n">
-        <v>4.15</v>
+        <v>3.35</v>
       </c>
       <c r="N106" t="n">
-        <v>5.4</v>
+        <v>2.15</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="Z106" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.5</v>
+        <v>3.63</v>
       </c>
       <c r="M107" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="N107" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,16 +14253,16 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AB107" t="n">
         <v>1.6</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB107" t="n">
-        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.56</v>
+        <v>1.85</v>
       </c>
       <c r="M108" t="n">
-        <v>3.94</v>
+        <v>3.65</v>
       </c>
       <c r="N108" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="Z108" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14818,12 +14818,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.11</v>
+        <v>2.19</v>
       </c>
       <c r="M112" t="n">
-        <v>8.5</v>
+        <v>3.29</v>
       </c>
       <c r="N112" t="n">
-        <v>28</v>
+        <v>3.23</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,16 +14898,16 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA112" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC112" t="n">
         <v>0</v>
@@ -14938,7 +14938,7 @@
         <v>0</v>
       </c>
       <c r="AK112" s="3" t="n">
-        <v>45926.67708333334</v>
+        <v>45926.66666666666</v>
       </c>
     </row>
     <row r="113">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15033,10 +15033,10 @@
         <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB113" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45926.6875</v>
+        <v>45926.67708333334</v>
       </c>
     </row>
     <row r="114">
@@ -15076,27 +15076,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45926.79166666666</v>
+        <v>45926.6875</v>
       </c>
     </row>
     <row r="115">
@@ -15205,12 +15205,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45926.83333333334</v>
+        <v>45926.79166666666</v>
       </c>
     </row>
     <row r="116">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15463,12 +15463,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15583,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="AK117" s="3" t="n">
-        <v>45926.875</v>
+        <v>45926.83333333334</v>
       </c>
     </row>
     <row r="118">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="M118" t="n">
-        <v>5.2</v>
+        <v>3.55</v>
       </c>
       <c r="N118" t="n">
-        <v>8.5</v>
+        <v>3.9</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="Z118" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15721,12 +15721,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AK119" s="3" t="n">
-        <v>45926.89583333334</v>
+        <v>45926.875</v>
       </c>
     </row>
     <row r="120">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45926.91666666666</v>
+        <v>45926.89583333334</v>
       </c>
     </row>
     <row r="121">
@@ -15979,126 +15979,255 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M121" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N121" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK121" s="3" t="n">
+        <v>45926.91666666666</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>45926</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
           <t>23:30</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
+      <c r="E122" t="inlineStr">
         <is>
           <t>San Diego Wave</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>Orlando Pride</t>
         </is>
       </c>
-      <c r="G121" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" t="inlineStr">
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L121" t="n">
+      <c r="L122" t="n">
         <v>2.08</v>
       </c>
-      <c r="M121" t="n">
+      <c r="M122" t="n">
         <v>3.4</v>
       </c>
-      <c r="N121" t="n">
+      <c r="N122" t="n">
         <v>3.25</v>
       </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="P121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" t="n">
-        <v>0</v>
-      </c>
-      <c r="W121" t="n">
-        <v>0</v>
-      </c>
-      <c r="X121" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y121" t="n">
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y122" t="n">
         <v>1.9</v>
       </c>
-      <c r="Z121" t="n">
+      <c r="Z122" t="n">
         <v>1.8</v>
       </c>
-      <c r="AA121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK121" s="3" t="n">
+      <c r="AA122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK122" s="3" t="n">
         <v>45926.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -708,10 +708,10 @@
         <v>3.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AA2" t="n">
         <v>2.62</v>
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -972,10 +972,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.85</v>
+        <v>3.55</v>
       </c>
       <c r="M5" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1581,40 +1581,40 @@
         <v>8.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA9" t="n">
         <v>1.85</v>
@@ -1623,10 +1623,10 @@
         <v>1.95</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1710,40 +1710,40 @@
         <v>16</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA10" t="n">
         <v>1.85</v>
@@ -1752,10 +1752,10 @@
         <v>1.95</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.12</v>
+        <v>3.72</v>
       </c>
       <c r="M12" t="n">
-        <v>3.27</v>
+        <v>3.93</v>
       </c>
       <c r="N12" t="n">
-        <v>2.93</v>
+        <v>1.75</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.89</v>
+        <v>2.55</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="Z16" t="n">
         <v>1.95</v>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.87</v>
+        <v>2.42</v>
       </c>
       <c r="M27" t="n">
-        <v>3.66</v>
+        <v>3.29</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.15</v>
+        <v>1.58</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.75</v>
+        <v>1.55</v>
       </c>
       <c r="M30" t="n">
-        <v>3.51</v>
+        <v>4.2</v>
       </c>
       <c r="N30" t="n">
-        <v>1.93</v>
+        <v>5.1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="M32" t="n">
-        <v>4.2</v>
+        <v>3.66</v>
       </c>
       <c r="N32" t="n">
-        <v>5.1</v>
+        <v>3.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="M40" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="N40" t="n">
-        <v>2.85</v>
+        <v>8</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.89</v>
+        <v>2.43</v>
       </c>
       <c r="M42" t="n">
-        <v>3.34</v>
+        <v>3.81</v>
       </c>
       <c r="N42" t="n">
-        <v>3.45</v>
+        <v>2.24</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.43</v>
+        <v>1.89</v>
       </c>
       <c r="M44" t="n">
-        <v>3.81</v>
+        <v>3.34</v>
       </c>
       <c r="N44" t="n">
-        <v>2.24</v>
+        <v>3.45</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="M47" t="n">
-        <v>5.1</v>
+        <v>3.93</v>
       </c>
       <c r="N47" t="n">
-        <v>5.7</v>
+        <v>4.33</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="M48" t="n">
-        <v>3.93</v>
+        <v>3.95</v>
       </c>
       <c r="N48" t="n">
-        <v>4.33</v>
+        <v>2.85</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6777,10 +6777,10 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6993,10 +6993,10 @@
         <v>1.94</v>
       </c>
       <c r="M51" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="N51" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,16 +7029,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,16 +7287,16 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leixões</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Leixões</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.31</v>
+        <v>1.82</v>
       </c>
       <c r="M59" t="n">
-        <v>3.21</v>
+        <v>3.35</v>
       </c>
       <c r="N59" t="n">
-        <v>1.97</v>
+        <v>4.3</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,49 +8151,49 @@
         </is>
       </c>
       <c r="L60" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N60" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z60" t="n">
         <v>1.68</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N60" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>1.73</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8276,17 +8276,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.44</v>
+        <v>3.3</v>
       </c>
       <c r="M62" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N62" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="M63" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N63" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="M64" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="N64" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="M65" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N65" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8838,7 +8838,7 @@
         <v>2.35</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="M66" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="N66" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="M67" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N67" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9179,17 +9179,17 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="M69" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N69" t="n">
-        <v>3.85</v>
+        <v>2.4</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10647,10 +10647,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="M81" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="N81" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11034,10 +11034,10 @@
         <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,16 +11286,16 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.8</v>
+        <v>1.52</v>
       </c>
       <c r="M88" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="N88" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,16 +11802,16 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC88" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>3.02</v>
+        <v>1.93</v>
       </c>
       <c r="M91" t="n">
-        <v>3.12</v>
+        <v>3.41</v>
       </c>
       <c r="N91" t="n">
-        <v>2.39</v>
+        <v>3.23</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.93</v>
+        <v>1.08</v>
       </c>
       <c r="M92" t="n">
-        <v>3.41</v>
+        <v>12</v>
       </c>
       <c r="N92" t="n">
-        <v>3.23</v>
+        <v>19</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,16 +12318,16 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.78</v>
+        <v>1.18</v>
       </c>
       <c r="Z92" t="n">
-        <v>2.03</v>
+        <v>4.75</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.08</v>
+        <v>3.02</v>
       </c>
       <c r="M93" t="n">
-        <v>12</v>
+        <v>3.12</v>
       </c>
       <c r="N93" t="n">
-        <v>19</v>
+        <v>2.39</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,16 +12447,16 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.18</v>
+        <v>2.2</v>
       </c>
       <c r="Z93" t="n">
-        <v>4.75</v>
+        <v>1.68</v>
       </c>
       <c r="AA93" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
         <v>0</v>
@@ -12630,22 +12630,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
       <c r="M95" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="N95" t="n">
-        <v>2.65</v>
+        <v>1.35</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="M96" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N96" t="n">
-        <v>2.25</v>
+        <v>1.42</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="Z96" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.58</v>
+        <v>2.5</v>
       </c>
       <c r="M97" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="N97" t="n">
-        <v>5.1</v>
+        <v>2.45</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,22 +13017,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>7.2</v>
+        <v>1.58</v>
       </c>
       <c r="M98" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="N98" t="n">
-        <v>1.35</v>
+        <v>5.1</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Z98" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="M101" t="n">
         <v>3.65</v>
       </c>
       <c r="N101" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="Z101" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="M102" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="N102" t="n">
-        <v>1.42</v>
+        <v>2.25</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="M103" t="n">
-        <v>3.94</v>
+        <v>4.15</v>
       </c>
       <c r="N103" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="Z103" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,55 +13827,55 @@
         </is>
       </c>
       <c r="L104" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="M104" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="N104" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>0</v>
+      </c>
+      <c r="U104" t="n">
+        <v>0</v>
+      </c>
+      <c r="V104" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AB104" t="n">
         <v>1.6</v>
-      </c>
-      <c r="M104" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="N104" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" t="n">
-        <v>0</v>
-      </c>
-      <c r="S104" t="n">
-        <v>0</v>
-      </c>
-      <c r="T104" t="n">
-        <v>0</v>
-      </c>
-      <c r="U104" t="n">
-        <v>0</v>
-      </c>
-      <c r="V104" t="n">
-        <v>0</v>
-      </c>
-      <c r="W104" t="n">
-        <v>0</v>
-      </c>
-      <c r="X104" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y104" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z104" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB104" t="n">
-        <v>0</v>
       </c>
       <c r="AC104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="M105" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="N105" t="n">
-        <v>5.6</v>
+        <v>2.65</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Z105" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,16 +14253,16 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="M108" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="N108" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="M118" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="N118" t="n">
-        <v>3.9</v>
+        <v>8.5</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="M119" t="n">
-        <v>5.2</v>
+        <v>3.55</v>
       </c>
       <c r="N119" t="n">
-        <v>8.5</v>
+        <v>3.9</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="Z119" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>

--- a/jogos_2025-09-26.xlsx
+++ b/jogos_2025-09-26.xlsx
@@ -762,22 +762,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mathare United</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Mathare United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O7" t="n">
         <v>3.02</v>
@@ -1350,13 +1350,13 @@
         <v>1.29</v>
       </c>
       <c r="X7" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AA7" t="n">
         <v>3.45</v>
@@ -1368,7 +1368,7 @@
         <v>1.77</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH7" t="n">
         <v>1.46</v>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.88</v>
+        <v>3.55</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
-        <v>3.65</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>2.38</v>
+        <v>4.32</v>
       </c>
       <c r="P8" t="n">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.4</v>
+        <v>2.64</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>2.99</v>
+        <v>2.55</v>
       </c>
       <c r="T8" t="n">
-        <v>2.48</v>
+        <v>3.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="W8" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="X8" t="n">
-        <v>3.58</v>
+        <v>2.78</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.94</v>
+        <v>1.65</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.85</v>
+        <v>3.75</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.82</v>
+        <v>1.24</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.72</v>
+        <v>2.12</v>
       </c>
       <c r="M10" t="n">
-        <v>3.93</v>
+        <v>3.27</v>
       </c>
       <c r="N10" t="n">
-        <v>1.75</v>
+        <v>2.93</v>
       </c>
       <c r="O10" t="n">
-        <v>4.4</v>
+        <v>2.84</v>
       </c>
       <c r="P10" t="n">
-        <v>2.61</v>
+        <v>2.07</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.23</v>
+        <v>3.58</v>
       </c>
       <c r="R10" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="S10" t="n">
-        <v>3.66</v>
+        <v>2.94</v>
       </c>
       <c r="T10" t="n">
-        <v>2.14</v>
+        <v>2.91</v>
       </c>
       <c r="U10" t="n">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="X10" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.55</v>
+        <v>1.89</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>3.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.62</v>
+        <v>1.27</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.3</v>
+        <v>3.72</v>
       </c>
       <c r="M13" t="n">
-        <v>3.29</v>
+        <v>3.93</v>
       </c>
       <c r="N13" t="n">
-        <v>2.86</v>
+        <v>1.75</v>
       </c>
       <c r="O13" t="n">
-        <v>2.84</v>
+        <v>4.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.19</v>
+        <v>2.61</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.58</v>
+        <v>2.23</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="S13" t="n">
-        <v>2.94</v>
+        <v>3.66</v>
       </c>
       <c r="T13" t="n">
-        <v>2.91</v>
+        <v>2.14</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.66</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W13" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="X13" t="n">
-        <v>3.41</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.24</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DPMM FC</t>
+          <t>Ha Noi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kelantan United</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ha Noi</t>
+          <t>DPMM FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Kelantan United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2604,16 +2604,16 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
         <v>2.3</v>
       </c>
       <c r="O17" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
         <v>2.15</v>
@@ -2643,7 +2643,7 @@
         <v>3.75</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Z17" t="n">
         <v>1.95</v>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sepahan</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Sepahan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Selangor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="N27" t="n">
-        <v>4.4</v>
+        <v>3.54</v>
       </c>
       <c r="O27" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="P27" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.4</v>
+        <v>4.03</v>
       </c>
       <c r="R27" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>3.64</v>
+        <v>3.28</v>
       </c>
       <c r="T27" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="U27" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W27" t="n">
         <v>1.15</v>
       </c>
       <c r="X27" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Selangor</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Kudrivka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Epitsentr Dunayivtsi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="Y31" t="n">
         <v>2.25</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Z31" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AA31" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Epitsentr Dunayivtsi</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.42</v>
+        <v>1.55</v>
       </c>
       <c r="M32" t="n">
-        <v>3.29</v>
+        <v>4.2</v>
       </c>
       <c r="N32" t="n">
-        <v>2.84</v>
+        <v>5.1</v>
       </c>
       <c r="O32" t="n">
-        <v>3.24</v>
+        <v>2.15</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>2.56</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.72</v>
+        <v>4.4</v>
       </c>
       <c r="R32" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>2.52</v>
+        <v>3.64</v>
       </c>
       <c r="T32" t="n">
-        <v>3.3</v>
+        <v>2.19</v>
       </c>
       <c r="U32" t="n">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="V32" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.37</v>
+        <v>1.15</v>
       </c>
       <c r="X32" t="n">
-        <v>2.67</v>
+        <v>4.9</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA32" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AB32" t="n">
         <v>1.58</v>
       </c>
-      <c r="AA32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AC32" t="n">
-        <v>2</v>
+        <v>1.48</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.74</v>
+        <v>2.38</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.55</v>
+        <v>2.12</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4797,77 +4797,77 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>3.51</v>
       </c>
       <c r="N34" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="O34" t="n">
         <v>4.3</v>
       </c>
       <c r="P34" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="R34" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S34" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="T34" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="U34" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="V34" t="n">
         <v>1</v>
       </c>
       <c r="W34" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X34" t="n">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Z34" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
         <v>1.89</v>
       </c>
-      <c r="AA34" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AB34" t="n">
+      <c r="AH34" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.29</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5313,22 +5313,22 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="M38" t="n">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="N38" t="n">
-        <v>3.65</v>
+        <v>3.11</v>
       </c>
       <c r="O38" t="n">
         <v>2.64</v>
       </c>
       <c r="P38" t="n">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.35</v>
+        <v>3.78</v>
       </c>
       <c r="R38" t="n">
         <v>1.33</v>
@@ -5349,7 +5349,7 @@
         <v>1.22</v>
       </c>
       <c r="X38" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="Y38" t="n">
         <v>1.85</v>
@@ -5361,7 +5361,7 @@
         <v>2.8</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AC38" t="n">
         <v>1.62</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,61 +5700,61 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,61 +5829,61 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.34</v>
+        <v>1.89</v>
       </c>
       <c r="M42" t="n">
-        <v>5.1</v>
+        <v>3.34</v>
       </c>
       <c r="N42" t="n">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="O42" t="n">
-        <v>1.67</v>
+        <v>2.73</v>
       </c>
       <c r="P42" t="n">
-        <v>2.85</v>
+        <v>2.16</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.45</v>
+        <v>4.05</v>
       </c>
       <c r="R42" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="S42" t="n">
-        <v>4.2</v>
+        <v>2.65</v>
       </c>
       <c r="T42" t="n">
-        <v>1.93</v>
+        <v>2.9</v>
       </c>
       <c r="U42" t="n">
-        <v>1.77</v>
+        <v>1.35</v>
       </c>
       <c r="V42" t="n">
         <v>1.01</v>
       </c>
       <c r="W42" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="X42" t="n">
-        <v>6.46</v>
+        <v>3.04</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.32</v>
+        <v>1.95</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.88</v>
+        <v>1.75</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="AB42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC42" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC42" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AD42" t="n">
-        <v>2.19</v>
+        <v>1.85</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="AH42" t="n">
-        <v>3.34</v>
+        <v>1.7</v>
       </c>
       <c r="AI42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,61 +5958,61 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,61 +6087,61 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="M44" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="N44" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="O44" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="P44" t="n">
-        <v>2.94</v>
+        <v>2.64</v>
       </c>
       <c r="Q44" t="n">
-        <v>8.92</v>
+        <v>5.03</v>
       </c>
       <c r="R44" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S44" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="T44" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="U44" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V44" t="n">
         <v>1.01</v>
       </c>
       <c r="W44" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X44" t="n">
-        <v>5.8</v>
+        <v>6.46</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.91</v>
+        <v>1.63</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.7</v>
+        <v>2.24</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AH44" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,61 +6216,61 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="M45" t="n">
-        <v>3.34</v>
+        <v>3.95</v>
       </c>
       <c r="N45" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="O45" t="n">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.17</v>
+        <v>3.05</v>
       </c>
       <c r="R45" t="n">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="S45" t="n">
-        <v>2.65</v>
+        <v>3.84</v>
       </c>
       <c r="T45" t="n">
-        <v>2.9</v>
+        <v>2.09</v>
       </c>
       <c r="U45" t="n">
-        <v>1.35</v>
+        <v>1.69</v>
       </c>
       <c r="V45" t="n">
         <v>1.01</v>
       </c>
       <c r="W45" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="X45" t="n">
-        <v>3.04</v>
+        <v>5.5</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.95</v>
+        <v>1.39</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.75</v>
+        <v>2.59</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.6</v>
+        <v>2.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.23</v>
+        <v>1.68</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.85</v>
+        <v>2.6</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AI45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="M46" t="n">
-        <v>3.53</v>
+        <v>3.93</v>
       </c>
       <c r="N46" t="n">
-        <v>3.78</v>
+        <v>4.33</v>
       </c>
       <c r="O46" t="n">
-        <v>2.36</v>
+        <v>2.15</v>
       </c>
       <c r="P46" t="n">
-        <v>2.19</v>
+        <v>2.31</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.55</v>
+        <v>5.08</v>
       </c>
       <c r="R46" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="S46" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="T46" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="U46" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="V46" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W46" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="X46" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.94</v>
+        <v>2.53</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.57</v>
+        <v>1.23</v>
       </c>
       <c r="M47" t="n">
-        <v>3.93</v>
+        <v>6.7</v>
       </c>
       <c r="N47" t="n">
-        <v>4.33</v>
+        <v>11</v>
       </c>
       <c r="O47" t="n">
-        <v>2.14</v>
+        <v>1.68</v>
       </c>
       <c r="P47" t="n">
-        <v>2.32</v>
+        <v>2.78</v>
       </c>
       <c r="Q47" t="n">
-        <v>5.08</v>
+        <v>7.76</v>
       </c>
       <c r="R47" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="S47" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="T47" t="n">
-        <v>2.48</v>
+        <v>2.16</v>
       </c>
       <c r="U47" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="V47" t="n">
         <v>1.02</v>
       </c>
       <c r="W47" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="X47" t="n">
-        <v>4.3</v>
+        <v>5.25</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.5</v>
+        <v>1.97</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.06</v>
+        <v>3.8</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,61 +6732,61 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
@@ -6799,10 +6799,10 @@
         </is>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,61 +6861,61 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
@@ -6928,10 +6928,10 @@
         </is>
       </c>
       <c r="AG50" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,61 +7377,61 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AD54" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
@@ -7444,10 +7444,10 @@
         </is>
       </c>
       <c r="AG54" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,77 +7506,77 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.75</v>
+        <v>3.31</v>
       </c>
       <c r="M55" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="N55" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="O55" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="R55" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S55" t="n">
         <v>2.5</v>
       </c>
-      <c r="O55" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="P55" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="R55" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.76</v>
-      </c>
       <c r="T55" t="n">
-        <v>2.69</v>
+        <v>3.22</v>
       </c>
       <c r="U55" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="V55" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W55" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="X55" t="n">
-        <v>3.34</v>
+        <v>2.67</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.97</v>
+        <v>4.1</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AC55" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD55" t="n">
         <v>1.66</v>
       </c>
-      <c r="AD55" t="n">
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
         <v>2.07</v>
       </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG55" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH55" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Stuttgart II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,77 +7635,77 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>3.31</v>
+        <v>1.65</v>
       </c>
       <c r="M56" t="n">
-        <v>3.21</v>
+        <v>3.97</v>
       </c>
       <c r="N56" t="n">
-        <v>1.97</v>
+        <v>4.1</v>
       </c>
       <c r="O56" t="n">
-        <v>5.6</v>
+        <v>2.2</v>
       </c>
       <c r="P56" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.35</v>
+        <v>4.42</v>
       </c>
       <c r="R56" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="S56" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="T56" t="n">
-        <v>3.22</v>
+        <v>2.29</v>
       </c>
       <c r="U56" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="V56" t="n">
         <v>1.03</v>
       </c>
       <c r="W56" t="n">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="X56" t="n">
-        <v>2.67</v>
+        <v>4.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.67</v>
+        <v>2.33</v>
       </c>
       <c r="AA56" t="n">
-        <v>4.1</v>
+        <v>2.28</v>
       </c>
       <c r="AB56" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
         <v>1.2</v>
       </c>
-      <c r="AC56" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG56" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AH56" t="n">
-        <v>1.16</v>
+        <v>1.94</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuttgart II</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,61 +7764,61 @@
         </is>
       </c>
       <c r="L57" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="M57" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="O57" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S57" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U57" t="n">
         <v>1.65</v>
       </c>
-      <c r="M57" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="N57" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O57" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P57" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S57" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.58</v>
-      </c>
       <c r="V57" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W57" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X57" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AA57" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AD57" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
@@ -7831,10 +7831,10 @@
         </is>
       </c>
       <c r="AG57" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.94</v>
+        <v>1.09</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,61 +7893,61 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U58" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,61 +8022,61 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI59" t="n">
         <v>0</v>
@@ -8421,22 +8421,22 @@
         <v>2.22</v>
       </c>
       <c r="P62" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="Q62" t="n">
-        <v>6.08</v>
+        <v>5.99</v>
       </c>
       <c r="R62" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S62" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="T62" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="U62" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V62" t="n">
         <v>1.03</v>
@@ -8445,7 +8445,7 @@
         <v>1.37</v>
       </c>
       <c r="X62" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="Y62" t="n">
         <v>2.05</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,61 +8538,61 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.44</v>
+        <v>3.3</v>
       </c>
       <c r="M63" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N63" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="O63" t="n">
-        <v>2.83</v>
+        <v>4.08</v>
       </c>
       <c r="P63" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.18</v>
+        <v>2.81</v>
       </c>
       <c r="R63" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S63" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W63" t="n">
         <v>1.3</v>
       </c>
-      <c r="S63" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T63" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="U63" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V63" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.16</v>
-      </c>
       <c r="X63" t="n">
-        <v>4.05</v>
+        <v>2.97</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AA63" t="n">
-        <v>2.64</v>
+        <v>3.58</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.45</v>
+        <v>1.21</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
       <c r="AD63" t="n">
-        <v>2.34</v>
+        <v>1.88</v>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
@@ -8605,10 +8605,10 @@
         </is>
       </c>
       <c r="AG63" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="M64" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="N64" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="O64" t="n">
-        <v>2.35</v>
+        <v>2.79</v>
       </c>
       <c r="P64" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Q64" t="n">
-        <v>5.58</v>
+        <v>4.7</v>
       </c>
       <c r="R64" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="S64" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="T64" t="n">
-        <v>3.26</v>
+        <v>3.65</v>
       </c>
       <c r="U64" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V64" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W64" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="X64" t="n">
-        <v>2.77</v>
+        <v>2.4</v>
       </c>
       <c r="Y64" t="n">
         <v>2.35</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AA64" t="n">
-        <v>4.05</v>
+        <v>5.1</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AC64" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8814,10 +8814,10 @@
         <v>4.9</v>
       </c>
       <c r="R65" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S65" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="T65" t="n">
         <v>2.98</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,61 +8925,61 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="M66" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N66" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="O66" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="P66" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.75</v>
+        <v>5.35</v>
       </c>
       <c r="R66" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="S66" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="T66" t="n">
-        <v>3.65</v>
+        <v>3.26</v>
       </c>
       <c r="U66" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="V66" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W66" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="X66" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="Y66" t="n">
         <v>2.35</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AA66" t="n">
-        <v>5.2</v>
+        <v>4.05</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AC66" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
@@ -8992,10 +8992,10 @@
         </is>
       </c>
       <c r="AG66" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -9063,16 +9063,16 @@
         <v>5</v>
       </c>
       <c r="O67" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="P67" t="n">
         <v>2.02</v>
       </c>
       <c r="Q67" t="n">
-        <v>5.23</v>
+        <v>5.22</v>
       </c>
       <c r="R67" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S67" t="n">
         <v>2.62</v>
@@ -9090,7 +9090,7 @@
         <v>1.32</v>
       </c>
       <c r="X67" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="Y67" t="n">
         <v>2.02</v>
@@ -9102,7 +9102,7 @@
         <v>3.95</v>
       </c>
       <c r="AB67" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AC67" t="n">
         <v>1.95</v>
@@ -9192,22 +9192,22 @@
         <v>5.3</v>
       </c>
       <c r="O68" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="P68" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="Q68" t="n">
         <v>4.8</v>
       </c>
       <c r="R68" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S68" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T68" t="n">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="U68" t="n">
         <v>1.34</v>
@@ -9219,7 +9219,7 @@
         <v>1.34</v>
       </c>
       <c r="X68" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="Y68" t="n">
         <v>2.12</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,61 +9312,61 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="M69" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N69" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="O69" t="n">
-        <v>4.08</v>
+        <v>2.48</v>
       </c>
       <c r="P69" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.76</v>
+        <v>5</v>
       </c>
       <c r="R69" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S69" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="T69" t="n">
-        <v>3.04</v>
+        <v>3.33</v>
       </c>
       <c r="U69" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V69" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W69" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X69" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AA69" t="n">
-        <v>3.58</v>
+        <v>4.35</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.81</v>
+        <v>2.01</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,61 +9441,61 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.7</v>
+        <v>2.44</v>
       </c>
       <c r="M70" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N70" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="O70" t="n">
-        <v>2.46</v>
+        <v>2.83</v>
       </c>
       <c r="P70" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="Q70" t="n">
-        <v>5</v>
+        <v>3.18</v>
       </c>
       <c r="R70" t="n">
-        <v>1.48</v>
+        <v>1.3</v>
       </c>
       <c r="S70" t="n">
-        <v>2.49</v>
+        <v>3.2</v>
       </c>
       <c r="T70" t="n">
-        <v>3.33</v>
+        <v>2.47</v>
       </c>
       <c r="U70" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="V70" t="n">
         <v>1.02</v>
       </c>
       <c r="W70" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="X70" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AA70" t="n">
-        <v>4.35</v>
+        <v>2.64</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="AC70" t="n">
-        <v>2.01</v>
+        <v>1.52</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.7</v>
+        <v>2.34</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
@@ -9508,10 +9508,10 @@
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.87</v>
+        <v>1.51</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,77 +9570,77 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="M71" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="N71" t="n">
-        <v>2.2</v>
+        <v>5.6</v>
       </c>
       <c r="O71" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>5</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S71" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X71" t="n">
         <v>3.48</v>
       </c>
-      <c r="P71" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R71" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S71" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T71" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U71" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V71" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W71" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X71" t="n">
-        <v>5</v>
-      </c>
       <c r="Y71" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="Z71" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG71" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH71" t="n">
         <v>2.35</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG71" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>1.38</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,61 +9699,61 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.51</v>
+        <v>1.36</v>
       </c>
       <c r="M72" t="n">
-        <v>3.7</v>
+        <v>5.33</v>
       </c>
       <c r="N72" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="P72" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S72" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X72" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA72" t="n">
         <v>1.89</v>
       </c>
-      <c r="O72" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="P72" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="R72" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S72" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T72" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U72" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V72" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W72" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X72" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z72" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AA72" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AB72" t="n">
-        <v>1.59</v>
+        <v>1.83</v>
       </c>
       <c r="AC72" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AD72" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="AG72" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AH72" t="n">
-        <v>1.31</v>
+        <v>2.82</v>
       </c>
       <c r="AI72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,61 +9828,61 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.7</v>
+        <v>3.51</v>
       </c>
       <c r="M73" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N73" t="n">
-        <v>2.6</v>
+        <v>1.89</v>
       </c>
       <c r="O73" t="n">
-        <v>3.38</v>
+        <v>3.78</v>
       </c>
       <c r="P73" t="n">
-        <v>2.06</v>
+        <v>2.4</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.22</v>
+        <v>2.42</v>
       </c>
       <c r="R73" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="S73" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="T73" t="n">
-        <v>2.93</v>
+        <v>2.02</v>
       </c>
       <c r="U73" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="V73" t="n">
         <v>1.02</v>
       </c>
       <c r="W73" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="X73" t="n">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.1</v>
+        <v>1.47</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.75</v>
+        <v>2.36</v>
       </c>
       <c r="AA73" t="n">
-        <v>3.55</v>
+        <v>2.4</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
@@ -9895,10 +9895,10 @@
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,61 +9957,61 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.72</v>
+        <v>1.37</v>
       </c>
       <c r="M74" t="n">
-        <v>3.51</v>
+        <v>5.1</v>
       </c>
       <c r="N74" t="n">
-        <v>2.37</v>
+        <v>7</v>
       </c>
       <c r="O74" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="P74" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.9</v>
+        <v>6.75</v>
       </c>
       <c r="R74" t="n">
         <v>1.25</v>
       </c>
       <c r="S74" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="T74" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="U74" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="V74" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W74" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X74" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="Z74" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="AA74" t="n">
-        <v>2.32</v>
+        <v>2.23</v>
       </c>
       <c r="AB74" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC74" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AD74" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="AE74" t="inlineStr">
         <is>
@@ -10024,10 +10024,10 @@
         </is>
       </c>
       <c r="AG74" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.49</v>
+        <v>3.15</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,61 +10086,61 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="M75" t="n">
         <v>3.25</v>
       </c>
       <c r="N75" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="O75" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="P75" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.68</v>
+        <v>2.45</v>
       </c>
       <c r="R75" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="S75" t="n">
-        <v>2.62</v>
+        <v>3.22</v>
       </c>
       <c r="T75" t="n">
-        <v>2.85</v>
+        <v>2.51</v>
       </c>
       <c r="U75" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="V75" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W75" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="X75" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="Y75" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="AA75" t="n">
-        <v>3.64</v>
+        <v>2.5</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AD75" t="n">
-        <v>1.85</v>
+        <v>2.28</v>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
@@ -10153,10 +10153,10 @@
         </is>
       </c>
       <c r="AG75" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,61 +10215,61 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.93</v>
+        <v>1.52</v>
       </c>
       <c r="M76" t="n">
-        <v>3.13</v>
+        <v>4.6</v>
       </c>
       <c r="N76" t="n">
-        <v>3.53</v>
+        <v>5.1</v>
       </c>
       <c r="O76" t="n">
-        <v>2.72</v>
+        <v>1.92</v>
       </c>
       <c r="P76" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="R76" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="S76" t="n">
-        <v>2.85</v>
+        <v>3.42</v>
       </c>
       <c r="T76" t="n">
-        <v>2.81</v>
+        <v>2.29</v>
       </c>
       <c r="U76" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="V76" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W76" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="X76" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.94</v>
+        <v>1.47</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="AA76" t="n">
-        <v>3.22</v>
+        <v>2.25</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.26</v>
+        <v>1.65</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AD76" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
@@ -10282,10 +10282,10 @@
         </is>
       </c>
       <c r="AG76" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.67</v>
+        <v>2.62</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,61 +10344,61 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="M77" t="n">
-        <v>3.61</v>
+        <v>3.35</v>
       </c>
       <c r="N77" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="O77" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="P77" t="n">
-        <v>2.53</v>
+        <v>2</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.13</v>
+        <v>3.68</v>
       </c>
       <c r="R77" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="S77" t="n">
-        <v>3.94</v>
+        <v>2.75</v>
       </c>
       <c r="T77" t="n">
-        <v>2.11</v>
+        <v>2.98</v>
       </c>
       <c r="U77" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="V77" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="W77" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="X77" t="n">
-        <v>5.65</v>
+        <v>3.1</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.39</v>
+        <v>2.1</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA77" t="n">
-        <v>2.12</v>
+        <v>3.64</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.71</v>
+        <v>1.25</v>
       </c>
       <c r="AC77" t="n">
-        <v>1.39</v>
+        <v>1.81</v>
       </c>
       <c r="AD77" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="AE77" t="inlineStr">
         <is>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="AG77" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,61 +10473,61 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="M78" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="N78" t="n">
-        <v>2.61</v>
+        <v>4.2</v>
       </c>
       <c r="O78" t="n">
-        <v>2.73</v>
+        <v>2.43</v>
       </c>
       <c r="P78" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.22</v>
+        <v>4.1</v>
       </c>
       <c r="R78" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S78" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V78" t="n">
+        <v>1</v>
+      </c>
+      <c r="W78" t="n">
         <v>1.24</v>
       </c>
-      <c r="S78" t="n">
+      <c r="X78" t="n">
         <v>3.7</v>
       </c>
-      <c r="T78" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U78" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V78" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W78" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X78" t="n">
-        <v>5.22</v>
-      </c>
       <c r="Y78" t="n">
-        <v>1.46</v>
+        <v>1.85</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.52</v>
+        <v>1.95</v>
       </c>
       <c r="AA78" t="n">
-        <v>2.25</v>
+        <v>2.92</v>
       </c>
       <c r="AB78" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AC78" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AD78" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
@@ -10540,10 +10540,10 @@
         </is>
       </c>
       <c r="AG78" t="n">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,61 +10602,61 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U79" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V79" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W79" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X79" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD79" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AE79" t="inlineStr">
         <is>
@@ -10669,10 +10669,10 @@
         </is>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,61 +10731,61 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="M80" t="n">
-        <v>3.69</v>
+        <v>3.9</v>
       </c>
       <c r="N80" t="n">
-        <v>4.3</v>
+        <v>2.61</v>
       </c>
       <c r="O80" t="n">
-        <v>2.05</v>
+        <v>2.73</v>
       </c>
       <c r="P80" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="Q80" t="n">
-        <v>5.15</v>
+        <v>3.22</v>
       </c>
       <c r="R80" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="S80" t="n">
-        <v>3.26</v>
+        <v>3.7</v>
       </c>
       <c r="T80" t="n">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="U80" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="V80" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W80" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X80" t="n">
-        <v>3.96</v>
+        <v>5.22</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.06</v>
+        <v>2.52</v>
       </c>
       <c r="AA80" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AD80" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AE80" t="inlineStr">
         <is>
@@ -10798,10 +10798,10 @@
         </is>
       </c>
       <c r="AG80" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="AH80" t="n">
-        <v>2.24</v>
+        <v>1.57</v>
       </c>
       <c r="AI80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,61 +10860,61 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>5.33</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>6.08</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,61 +10989,61 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="M82" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="N82" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="O82" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W82" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X82" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="AA82" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="inlineStr">
         <is>
@@ -11056,10 +11056,10 @@
         </is>
       </c>
       <c r="AG82" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,61 +11118,61 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="M83" t="n">
-        <v>5.1</v>
+        <v>3.69</v>
       </c>
       <c r="N83" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="O83" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="P83" t="n">
-        <v>2.8</v>
+        <v>2.31</v>
       </c>
       <c r="Q83" t="n">
-        <v>6.75</v>
+        <v>5.45</v>
       </c>
       <c r="R83" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="S83" t="n">
-        <v>3.66</v>
+        <v>3.26</v>
       </c>
       <c r="T83" t="n">
-        <v>2.18</v>
+        <v>2.41</v>
       </c>
       <c r="U83" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="V83" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W83" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="X83" t="n">
-        <v>5.25</v>
+        <v>3.97</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="Z83" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AA83" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AD83" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AE83" t="inlineStr">
         <is>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="AG83" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AH83" t="n">
-        <v>3.15</v>
+        <v>2.3</v>
       </c>
       <c r="AI83" t="n">
         <v>0</v>
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,61 +11247,61 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.75</v>
+        <v>2.34</v>
       </c>
       <c r="M84" t="n">
-        <v>3.7</v>
+        <v>3.61</v>
       </c>
       <c r="N84" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O84" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="P84" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="R84" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S84" t="n">
         <v>3.94</v>
       </c>
-      <c r="O84" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="P84" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>4</v>
-      </c>
-      <c r="R84" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S84" t="n">
-        <v>3.22</v>
-      </c>
       <c r="T84" t="n">
-        <v>2.44</v>
+        <v>2.11</v>
       </c>
       <c r="U84" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="V84" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W84" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X84" t="n">
-        <v>4.35</v>
+        <v>5.65</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="Z84" t="n">
-        <v>2.16</v>
+        <v>2.65</v>
       </c>
       <c r="AA84" t="n">
-        <v>2.56</v>
+        <v>2.12</v>
       </c>
       <c r="AB84" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="AD84" t="n">
-        <v>2.17</v>
+        <v>2.6</v>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>1.22</v>
       </c>
       <c r="AH84" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AI84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,61 +11376,61 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.8</v>
+        <v>2.72</v>
       </c>
       <c r="M85" t="n">
-        <v>3.75</v>
+        <v>3.51</v>
       </c>
       <c r="N85" t="n">
-        <v>4.2</v>
+        <v>2.37</v>
       </c>
       <c r="O85" t="n">
-        <v>2.43</v>
+        <v>3</v>
       </c>
       <c r="P85" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S85" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T85" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V85" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W85" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X85" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA85" t="n">
         <v>2.32</v>
       </c>
-      <c r="Q85" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="R85" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S85" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="T85" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="U85" t="n">
+      <c r="AB85" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC85" t="n">
         <v>1.44</v>
       </c>
-      <c r="V85" t="n">
-        <v>1</v>
-      </c>
-      <c r="W85" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X85" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA85" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AB85" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC85" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AD85" t="n">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="AE85" t="inlineStr">
         <is>
@@ -11443,10 +11443,10 @@
         </is>
       </c>
       <c r="AG85" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.9</v>
+        <v>1.49</v>
       </c>
       <c r="AI85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,61 +11505,61 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>3.8</v>
+        <v>1.75</v>
       </c>
       <c r="M86" t="n">
         <v>3.7</v>
       </c>
       <c r="N86" t="n">
-        <v>1.83</v>
+        <v>3.94</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W86" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Y86" t="n">
         <v>1.67</v>
       </c>
       <c r="Z86" t="n">
-        <v>2.07</v>
+        <v>2.16</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE86" t="inlineStr">
         <is>
@@ -11572,10 +11572,10 @@
         </is>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,61 +11634,61 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="M87" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="N87" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="O87" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P87" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R87" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S87" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T87" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V87" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W87" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X87" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y87" t="n">
         <v>2.1</v>
       </c>
-      <c r="P87" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="R87" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S87" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T87" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U87" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V87" t="n">
-        <v>1</v>
-      </c>
-      <c r="W87" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X87" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="Y87" t="n">
-        <v>1.9</v>
-      </c>
       <c r="Z87" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AA87" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AD87" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AE87" t="inlineStr">
         <is>
@@ -11701,10 +11701,10 @@
         </is>
       </c>
       <c r="AG87" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="AH87" t="n">
-        <v>2.35</v>
+        <v>1.4</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,61 +11763,61 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.52</v>
+        <v>1.93</v>
       </c>
       <c r="M88" t="n">
-        <v>4.6</v>
+        <v>3.13</v>
       </c>
       <c r="N88" t="n">
-        <v>5.1</v>
+        <v>3.53</v>
       </c>
       <c r="O88" t="n">
-        <v>1.92</v>
+        <v>2.75</v>
       </c>
       <c r="P88" t="n">
-        <v>2.45</v>
+        <v>2.09</v>
       </c>
       <c r="Q88" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="R88" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="S88" t="n">
-        <v>3.42</v>
+        <v>2.85</v>
       </c>
       <c r="T88" t="n">
-        <v>2.29</v>
+        <v>2.81</v>
       </c>
       <c r="U88" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="V88" t="n">
         <v>1.01</v>
       </c>
       <c r="W88" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="X88" t="n">
-        <v>5.1</v>
+        <v>3.28</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="Z88" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="AA88" t="n">
-        <v>2.25</v>
+        <v>3.22</v>
       </c>
       <c r="AB88" t="n">
-        <v>1.65</v>
+        <v>1.26</v>
       </c>
       <c r="AC88" t="n">
         <v>1.7</v>
       </c>
       <c r="AD88" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AE88" t="inlineStr">
         <is>
@@ -11830,10 +11830,10 @@
         </is>
       </c>
       <c r="AG88" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH88" t="n">
-        <v>2.62</v>
+        <v>1.69</v>
       </c>
       <c r="AI88" t="n">
         <v>0</v>
@@ -12030,13 +12030,13 @@
         <v>1.75</v>
       </c>
       <c r="O90" t="n">
-        <v>4.08</v>
+        <v>4.36</v>
       </c>
       <c r="P90" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="R90" t="n">
         <v>1.3</v>
@@ -12048,16 +12048,16 @@
         <v>2.44</v>
       </c>
       <c r="U90" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V90" t="n">
         <v>1.03</v>
       </c>
       <c r="W90" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X90" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y90" t="n">
         <v>1.68</v>
@@ -12075,7 +12075,7 @@
         <v>1.55</v>
       </c>
       <c r="AD90" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AE90" t="inlineStr">
         <is>
@@ -12088,10 +12088,10 @@
         </is>
       </c>
       <c r="AG90" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,61 +12150,61 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.99</v>
+        <v>2.65</v>
       </c>
       <c r="M91" t="n">
-        <v>3.39</v>
+        <v>3.17</v>
       </c>
       <c r="N91" t="n">
-        <v>3.11</v>
+        <v>2.66</v>
       </c>
       <c r="O91" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V91" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.57</v>
+        <v>2.3</v>
       </c>
       <c r="Z91" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="AA91" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD91" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
@@ -12217,10 +12217,10 @@
         </is>
       </c>
       <c r="AG91" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -12291,7 +12291,7 @@
         <v>1.36</v>
       </c>
       <c r="P92" t="n">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="Q92" t="n">
         <v>11</v>
@@ -12346,7 +12346,7 @@
         </is>
       </c>
       <c r="AG92" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AH92" t="n">
         <v>7</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,61 +12408,61 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.02</v>
+        <v>1.93</v>
       </c>
       <c r="M93" t="n">
-        <v>3.12</v>
+        <v>3.41</v>
       </c>
       <c r="N93" t="n">
-        <v>2.39</v>
+        <v>3.23</v>
       </c>
       <c r="O93" t="n">
-        <v>3.27</v>
+        <v>2.62</v>
       </c>
       <c r="P93" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R93" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S93" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="T93" t="n">
-        <v>3.35</v>
+        <v>2.59</v>
       </c>
       <c r="U93" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="V93" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W93" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="X93" t="n">
-        <v>2.74</v>
+        <v>4.2</v>
       </c>
       <c r="Y93" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.68</v>
+        <v>2.03</v>
       </c>
       <c r="AA93" t="n">
-        <v>4.2</v>
+        <v>2.65</v>
       </c>
       <c r="AB93" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AC93" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="AD93" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AE93" t="inlineStr">
         <is>
@@ -12475,10 +12475,10 @@
         </is>
       </c>
       <c r="AG93" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.51</v>
+        <v>1.78</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,61 +12537,61 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.65</v>
+        <v>3.02</v>
       </c>
       <c r="M94" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="N94" t="n">
-        <v>2.66</v>
+        <v>2.39</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S94" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="T94" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U94" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V94" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD94" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE94" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AG94" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH94" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,61 +12666,61 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="M95" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="N95" t="n">
-        <v>3.23</v>
+        <v>3.11</v>
       </c>
       <c r="O95" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="P95" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="Q95" t="n">
-        <v>4</v>
+        <v>3.57</v>
       </c>
       <c r="R95" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="S95" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="T95" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="U95" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="V95" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W95" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X95" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="Z95" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="AA95" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="AB95" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AC95" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AD95" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AE95" t="inlineStr">
         <is>
@@ -12733,10 +12733,10 @@
         </is>
       </c>
       <c r="AG95" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH95" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AI95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,61 +12795,61 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>3.45</v>
+        <v>1.5</v>
       </c>
       <c r="M96" t="n">
-        <v>3.35</v>
+        <v>4.09</v>
       </c>
       <c r="N96" t="n">
-        <v>2.15</v>
+        <v>4.66</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="V96" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W96" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X96" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.3</v>
+        <v>1.57</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.63</v>
+        <v>2.35</v>
       </c>
       <c r="AA96" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB96" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE96" t="inlineStr">
         <is>
@@ -12862,10 +12862,10 @@
         </is>
       </c>
       <c r="AG96" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH96" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
@@ -12924,61 +12924,61 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="M97" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="N97" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S97" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U97" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X97" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE97" t="inlineStr">
         <is>
@@ -12991,10 +12991,10 @@
         </is>
       </c>
       <c r="AG97" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH97" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI97" t="n">
         <v>0</v>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,61 +13053,61 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.55</v>
+        <v>3.45</v>
       </c>
       <c r="M98" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="N98" t="n">
-        <v>5.6</v>
+        <v>2.15</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V98" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="Z98" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AE98" t="inlineStr">
         <is>
@@ -13120,10 +13120,10 @@
         </is>
       </c>
       <c r="AG98" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH98" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI98" t="n">
         <v>0</v>
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,61 +13182,61 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.5</v>
+        <v>3.63</v>
       </c>
       <c r="M99" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="N99" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Y99" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AB99" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z99" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB99" t="n">
-        <v>0</v>
-      </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD99" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE99" t="inlineStr">
         <is>
@@ -13249,10 +13249,10 @@
         </is>
       </c>
       <c r="AG99" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH99" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI99" t="n">
         <v>0</v>
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,61 +13311,61 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M100" t="n">
-        <v>4.15</v>
+        <v>4.75</v>
       </c>
       <c r="N100" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U100" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V100" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W100" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="Z100" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE100" t="inlineStr">
         <is>
@@ -13378,10 +13378,10 @@
         </is>
       </c>
       <c r="AG100" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH100" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI100" t="n">
         <v>0</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,61 +13440,61 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>3.63</v>
+        <v>1.85</v>
       </c>
       <c r="M101" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="N101" t="n">
-        <v>1.91</v>
+        <v>4.2</v>
       </c>
       <c r="O101" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="P101" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="Q101" t="n">
-        <v>2.35</v>
+        <v>4.9</v>
       </c>
       <c r="R101" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="S101" t="n">
-        <v>3.24</v>
+        <v>2.71</v>
       </c>
       <c r="T101" t="n">
-        <v>2.47</v>
+        <v>3.1</v>
       </c>
       <c r="U101" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="V101" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="W101" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="X101" t="n">
-        <v>4.5</v>
+        <v>3.16</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="Z101" t="n">
-        <v>2.17</v>
+        <v>1.82</v>
       </c>
       <c r="AA101" t="n">
-        <v>2.34</v>
+        <v>3.4</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AD101" t="n">
-        <v>2.26</v>
+        <v>1.87</v>
       </c>
       <c r="AE101" t="inlineStr">
         <is>
@@ -13507,10 +13507,10 @@
         </is>
       </c>
       <c r="AG101" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AH101" t="n">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="AI101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,61 +13569,61 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="M102" t="n">
-        <v>3.45</v>
+        <v>4.15</v>
       </c>
       <c r="N102" t="n">
-        <v>2.65</v>
+        <v>5.4</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T102" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U102" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V102" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W102" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
@@ -13636,10 +13636,10 @@
         </is>
       </c>
       <c r="AG102" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH102" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI102" t="n">
         <v>0</v>
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,61 +13698,61 @@
         </is>
       </c>
       <c r="L103" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M103" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N103" t="n">
+        <v>5</v>
+      </c>
+      <c r="O103" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="P103" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="R103" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S103" t="n">
         <v>3</v>
       </c>
-      <c r="M103" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N103" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O103" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="P103" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R103" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S103" t="n">
-        <v>3.14</v>
-      </c>
       <c r="T103" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="U103" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V103" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W103" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="X103" t="n">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="Z103" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AA103" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AB103" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AD103" t="n">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="AE103" t="inlineStr">
         <is>
@@ -13765,10 +13765,10 @@
         </is>
       </c>
       <c r="AG103" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH103" t="n">
-        <v>1.38</v>
+        <v>2.11</v>
       </c>
       <c r="AI103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,61 +13827,61 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M104" t="n">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="N104" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S104" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U104" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V104" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W104" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X104" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="Z104" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD104" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AE104" t="inlineStr">
         <is>
@@ -13894,10 +13894,10 @@
         </is>
       </c>
       <c r="AG104" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AH104" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI104" t="n">
         <v>0</v>
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,61 +13956,61 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.59</v>
+        <v>2.45</v>
       </c>
       <c r="M105" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="N105" t="n">
-        <v>4.8</v>
+        <v>2.45</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S105" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="T105" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U105" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="V105" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W105" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.79</v>
+        <v>2.11</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC105" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD105" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE105" t="inlineStr">
         <is>
@@ -14023,10 +14023,10 @@
         </is>
       </c>
       <c r="AG105" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH105" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,61 +14085,61 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>6.5</v>
+        <v>2.45</v>
       </c>
       <c r="M106" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="N106" t="n">
-        <v>1.42</v>
+        <v>2.6</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T106" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U106" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W106" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X106" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC106" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD106" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE106" t="inlineStr">
         <is>
@@ -14152,10 +14152,10 @@
         </is>
       </c>
       <c r="AG106" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH106" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,22 +14214,22 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.85</v>
+        <v>6.5</v>
       </c>
       <c r="M107" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N107" t="n">
-        <v>4.2</v>
+        <v>1.42</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="R107" t="n">
         <v>0</v>
@@ -14238,37 +14238,37 @@
         <v>0</v>
       </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V107" t="n">
         <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X107" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE107" t="inlineStr">
         <is>
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="AG107" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH107" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,61 +14343,61 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T108" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U108" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V108" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W108" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD108" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE108" t="inlineStr">
         <is>
@@ -14410,10 +14410,10 @@
         </is>
       </c>
       <c r="AG108" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH108" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,77 +14472,77 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="M109" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="N109" t="n">
-        <v>1.35</v>
+        <v>2.25</v>
       </c>
       <c r="O109" t="n">
-        <v>6.1</v>
+        <v>3.45</v>
       </c>
       <c r="P109" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="Q109" t="n">
-        <v>1.83</v>
+        <v>2.8</v>
       </c>
       <c r="R109" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S109" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="T109" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="U109" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="V109" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W109" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="X109" t="n">
-        <v>3.96</v>
+        <v>4.2</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AA109" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AB109" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG109" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH109" t="n">
         <v>1.38</v>
-      </c>
-      <c r="AC109" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD109" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG109" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH109" t="n">
-        <v>1.05</v>
       </c>
       <c r="AI109" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,61 +14730,61 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S111" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U111" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V111" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W111" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA111" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC111" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AD111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE111" t="inlineStr">
         <is>
@@ -14797,10 +14797,10 @@
         </is>
       </c>
       <c r="AG111" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH111" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,61 +14988,61 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P113" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="T113" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U113" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V113" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AD113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE113" t="inlineStr">
         <is>
@@ -15055,10 +15055,10 @@
         </is>
       </c>
       <c r="AG113" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH113" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI113" t="n">
         <v>0</v>
@@ -15126,40 +15126,40 @@
         <v>28</v>
       </c>
       <c r="O114" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S114" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T114" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U114" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V114" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W114" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X114" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA114" t="n">
         <v>2.3</v>
@@ -15168,10 +15168,10 @@
         <v>1.6</v>
       </c>
       <c r="AC114" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AD114" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE114" t="inlineStr">
         <is>
@@ -15184,10 +15184,10 @@
         </is>
       </c>
       <c r="AG114" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH114" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AI114" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,61 +15375,61 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S116" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T116" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U116" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V116" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W116" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X116" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AA116" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="AB116" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AC116" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD116" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE116" t="inlineStr">
         <is>
@@ -15442,10 +15442,10 @@
         </is>
       </c>
       <c r="AG116" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH116" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AI116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>North Carolina FC</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Philadelphia Union II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>North Carolina FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Philadelphia Union II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.3</v>
+        <v>1.85</v>
       </c>
       <c r="M120" t="n">
-        <v>5.2</v>
+        <v>3.55</v>
       </c>
       <c r="N120" t="n">
-        <v>8.5</v>
+        <v>3.9</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="Z120" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="M121" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="N121" t="n">
-        <v>3.9</v>
+        <v>8.5</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
